--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R06af59610a58435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R3090e5bb7036416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R7feeeb0776514a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rf66106b63f394673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R7789883637444cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R9173e263e0184df3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -89,6 +89,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -8752,6 +8753,266 @@
         <x:v>Official / primary source</x:v>
       </x:c>
     </x:row>
+    <x:row r="425">
+      <x:c r="A425" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+      <x:c r="B425" s="14" t="str">
+        <x:v>Inocea</x:v>
+      </x:c>
+      <x:c r="C425" s="14" t="str">
+        <x:v>Group companies and facility overview</x:v>
+      </x:c>
+      <x:c r="D425" s="14" t="str">
+        <x:v>https://www.inocea.com/</x:v>
+      </x:c>
+      <x:c r="E425" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F425" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426" s="14" t="str">
+        <x:v>SRC_V1251_002</x:v>
+      </x:c>
+      <x:c r="B426" s="14" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="C426" s="14" t="str">
+        <x:v>Six Program Icebreakers contract and Inocea footprint</x:v>
+      </x:c>
+      <x:c r="D426" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+      <x:c r="E426" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F426" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427" s="14" t="str">
+        <x:v>SRC_V1251_003</x:v>
+      </x:c>
+      <x:c r="B427" s="14" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="C427" s="14" t="str">
+        <x:v>Helsinki Shipyard acquisition completion</x:v>
+      </x:c>
+      <x:c r="D427" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/davie-completes-purchase-of-the-assets-of-helsinki-shipyard/</x:v>
+      </x:c>
+      <x:c r="E427" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F427" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+      <x:c r="B428" s="14" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="C428" s="14" t="str">
+        <x:v>Davie Defense acquisition of Gulf Copper assets</x:v>
+      </x:c>
+      <x:c r="D428" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/davie-defense-closes-gulf-copper-acquisition-confirming-u-s-shipbuilding-expansion/</x:v>
+      </x:c>
+      <x:c r="E428" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F428" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429" s="14" t="str">
+        <x:v>SRC_V1251_005</x:v>
+      </x:c>
+      <x:c r="B429" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C429" s="14" t="str">
+        <x:v>CLI acquisition, ownership, terminals and metrics</x:v>
+      </x:c>
+      <x:c r="D429" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/06/02/ad-ports-group-acquires-cli</x:v>
+      </x:c>
+      <x:c r="E429" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F429" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430" s="14" t="str">
+        <x:v>SRC_V1251_006</x:v>
+      </x:c>
+      <x:c r="B430" s="14" t="str">
+        <x:v>Seaspan Corporation</x:v>
+      </x:c>
+      <x:c r="C430" s="14" t="str">
+        <x:v>Operating fleet and fleet capacity</x:v>
+      </x:c>
+      <x:c r="D430" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/operating-fleet/</x:v>
+      </x:c>
+      <x:c r="E430" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F430" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431" s="14" t="str">
+        <x:v>SRC_V1251_007</x:v>
+      </x:c>
+      <x:c r="B431" s="14" t="str">
+        <x:v>Seaspan Corporation</x:v>
+      </x:c>
+      <x:c r="C431" s="14" t="str">
+        <x:v>Seaspan-Maersk vessel upgrade programme</x:v>
+      </x:c>
+      <x:c r="D431" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/news/seaspan-and-maersk-advance-fleet-efficiency-through-strategic-vessel-upgrade-program/</x:v>
+      </x:c>
+      <x:c r="E431" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F431" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432" s="14" t="str">
+        <x:v>SRC_V1251_008</x:v>
+      </x:c>
+      <x:c r="B432" s="14" t="str">
+        <x:v>Seaspan ULC</x:v>
+      </x:c>
+      <x:c r="C432" s="14" t="str">
+        <x:v>Canadian Seaspan history and ownership</x:v>
+      </x:c>
+      <x:c r="D432" s="14" t="str">
+        <x:v>https://www.seaspan.com/who-we-are/our-history/</x:v>
+      </x:c>
+      <x:c r="E432" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F432" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433" s="14" t="str">
+        <x:v>SRC_V1251_009</x:v>
+      </x:c>
+      <x:c r="B433" s="14" t="str">
+        <x:v>Seaspan Corporation</x:v>
+      </x:c>
+      <x:c r="C433" s="14" t="str">
+        <x:v>KBRA investment-grade rating upgrade</x:v>
+      </x:c>
+      <x:c r="D433" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/news/seaspan-achieves-investment-grade-rating-upgrade-from-kbra/</x:v>
+      </x:c>
+      <x:c r="E433" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F433" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434" s="14" t="str">
+        <x:v>SRC_V1251_010</x:v>
+      </x:c>
+      <x:c r="B434" s="14" t="str">
+        <x:v>Macquarie Group</x:v>
+      </x:c>
+      <x:c r="C434" s="14" t="str">
+        <x:v>Qube acquisition completion</x:v>
+      </x:c>
+      <x:c r="D434" s="14" t="str">
+        <x:v>https://www.macquarie.com/li/en/about/news/2026/macquarie-asset-management-led-consortium-announces-successful-completion-of-qube-investment.html</x:v>
+      </x:c>
+      <x:c r="E434" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F434" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435" s="14" t="str">
+        <x:v>SRC_V1251_011</x:v>
+      </x:c>
+      <x:c r="B435" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C435" s="14" t="str">
+        <x:v>2025 annual report publication</x:v>
+      </x:c>
+      <x:c r="D435" s="14" t="str">
+        <x:v>https://wpvip.adportsgroup.com/adportsgroup/news-and-media/2026/03/30/ad-ports-group-publishes-2025-annual-report/</x:v>
+      </x:c>
+      <x:c r="E435" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F435" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436" s="14" t="str">
+        <x:v>SRC_V1251_012</x:v>
+      </x:c>
+      <x:c r="B436" s="14" t="str">
+        <x:v>AD Ports Group / ADX</x:v>
+      </x:c>
+      <x:c r="C436" s="14" t="str">
+        <x:v>2024 monthly share-price history</x:v>
+      </x:c>
+      <x:c r="D436" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="E436" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F436" s="14" t="str">
+        <x:v>Official annual report / exchange-hosted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437" s="14" t="str">
+        <x:v>SRC_V1251_013</x:v>
+      </x:c>
+      <x:c r="B437" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C437" s="14" t="str">
+        <x:v>2025 monthly share-price history</x:v>
+      </x:c>
+      <x:c r="D437" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="E437" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F437" s="14" t="str">
+        <x:v>Official annual report</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rf66106b63f394673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R7789883637444cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R9173e263e0184df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R79c78b547e5a4f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R5f979e33d1df4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R7f5f674e18754420"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9013,6 +9013,446 @@
         <x:v>Official annual report</x:v>
       </x:c>
     </x:row>
+    <x:row r="438">
+      <x:c r="A438" s="14" t="str">
+        <x:v>SRC126_001</x:v>
+      </x:c>
+      <x:c r="B438" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C438" s="14" t="str">
+        <x:v>Tbilisi Intermodal Hub facilities and gateway role</x:v>
+      </x:c>
+      <x:c r="D438" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2025/06/03/ad-ports-group-inaugurates-tbilisi-intermodal-hub-in-georgia</x:v>
+      </x:c>
+      <x:c r="E438" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F438" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439" s="14" t="str">
+        <x:v>SRC126_002</x:v>
+      </x:c>
+      <x:c r="B439" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C439" s="14" t="str">
+        <x:v>Constanța framework; GulfLink; Kuryk</x:v>
+      </x:c>
+      <x:c r="D439" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/04/14/ad-ports-group-signs-agreement-to-explore-investment-opportunities-in-the-port-of-constanta</x:v>
+      </x:c>
+      <x:c r="E439" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F439" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440" s="14" t="str">
+        <x:v>SRC126_003</x:v>
+      </x:c>
+      <x:c r="B440" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="C440" s="14" t="str">
+        <x:v>GulfLink ownership / Central Asia developments</x:v>
+      </x:c>
+      <x:c r="D440" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2025/08/13/ad-ports-group-delivers-strong-q2-2025-results</x:v>
+      </x:c>
+      <x:c r="E440" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F440" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441" s="14" t="str">
+        <x:v>SRC126_004</x:v>
+      </x:c>
+      <x:c r="B441" s="14" t="str">
+        <x:v>Port of Rotterdam Authority</x:v>
+      </x:c>
+      <x:c r="C441" s="14" t="str">
+        <x:v>Container Exchange Route</x:v>
+      </x:c>
+      <x:c r="D441" s="14" t="str">
+        <x:v>https://www.portofrotterdam.com/en/news-and-press-releases/the-port-of-rotterdam-authority-officially-commissions-container-exchange</x:v>
+      </x:c>
+      <x:c r="E441" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F441" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442" s="14" t="str">
+        <x:v>SRC126_005</x:v>
+      </x:c>
+      <x:c r="B442" s="14" t="str">
+        <x:v>Prince Rupert Port Authority</x:v>
+      </x:c>
+      <x:c r="C442" s="14" t="str">
+        <x:v>Fairview / CN on-dock rail</x:v>
+      </x:c>
+      <x:c r="D442" s="14" t="str">
+        <x:v>https://www.rupertport.com/terminal_details/fairview-container-terminal/</x:v>
+      </x:c>
+      <x:c r="E442" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F442" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443" s="14" t="str">
+        <x:v>SRC126_006</x:v>
+      </x:c>
+      <x:c r="B443" s="14" t="str">
+        <x:v>Maritime and Port Authority of Singapore</x:v>
+      </x:c>
+      <x:c r="C443" s="14" t="str">
+        <x:v>Singapore terminals / operators</x:v>
+      </x:c>
+      <x:c r="D443" s="14" t="str">
+        <x:v>https://www.mpa.gov.sg/port-marine-ops/operations/port-infrastructure/terminals</x:v>
+      </x:c>
+      <x:c r="E443" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F443" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444" s="14" t="str">
+        <x:v>SRC126_007</x:v>
+      </x:c>
+      <x:c r="B444" s="14" t="str">
+        <x:v>Shanghai International Port Group</x:v>
+      </x:c>
+      <x:c r="C444" s="14" t="str">
+        <x:v>SIPG / Shanghai public terminals</x:v>
+      </x:c>
+      <x:c r="D444" s="14" t="str">
+        <x:v>https://en.portshanghai.com.cn/AboutUs/index.jhtml</x:v>
+      </x:c>
+      <x:c r="E444" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F444" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445" s="14" t="str">
+        <x:v>SRC126_008</x:v>
+      </x:c>
+      <x:c r="B445" s="14" t="str">
+        <x:v>Port of Tallinn</x:v>
+      </x:c>
+      <x:c r="C445" s="14" t="str">
+        <x:v>Muuga / terminal operators</x:v>
+      </x:c>
+      <x:c r="D445" s="14" t="str">
+        <x:v>https://www.ts.ee/en/terminal-operators/</x:v>
+      </x:c>
+      <x:c r="E445" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F445" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446" s="14" t="str">
+        <x:v>SRC126_009</x:v>
+      </x:c>
+      <x:c r="B446" s="14" t="str">
+        <x:v>Klaipėda State Seaport Authority</x:v>
+      </x:c>
+      <x:c r="C446" s="14" t="str">
+        <x:v>Landlord governance model</x:v>
+      </x:c>
+      <x:c r="D446" s="14" t="str">
+        <x:v>https://portofklaipeda.lt/wp-content/uploads/2025/04/KVJUD-VA-and-FA-2024-EN-1.pdf</x:v>
+      </x:c>
+      <x:c r="E446" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F446" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" s="14" t="str">
+        <x:v>SRC126_010</x:v>
+      </x:c>
+      <x:c r="B447" s="14" t="str">
+        <x:v>Port of Gdańsk</x:v>
+      </x:c>
+      <x:c r="C447" s="14" t="str">
+        <x:v>Baltic Hub terminal</x:v>
+      </x:c>
+      <x:c r="D447" s="14" t="str">
+        <x:v>https://www.portgdansk.pl/en/about-port/terminals-and-quays/baltic-hub-container-terminal/</x:v>
+      </x:c>
+      <x:c r="E447" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F447" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" s="14" t="str">
+        <x:v>SRC126_011</x:v>
+      </x:c>
+      <x:c r="B448" s="14" t="str">
+        <x:v>Port of Gothenburg</x:v>
+      </x:c>
+      <x:c r="C448" s="14" t="str">
+        <x:v>Terminals / rail facilities</x:v>
+      </x:c>
+      <x:c r="D448" s="14" t="str">
+        <x:v>https://www.portofgothenburg.com/maritime/terminals/railway-terminals/</x:v>
+      </x:c>
+      <x:c r="E448" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F448" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" s="14" t="str">
+        <x:v>SRC126_012</x:v>
+      </x:c>
+      <x:c r="B449" s="14" t="str">
+        <x:v>DP World</x:v>
+      </x:c>
+      <x:c r="C449" s="14" t="str">
+        <x:v>Constanța rail / canal interface</x:v>
+      </x:c>
+      <x:c r="D449" s="14" t="str">
+        <x:v>https://www.dpworld.com/en/ports-terminals/romania/constanta</x:v>
+      </x:c>
+      <x:c r="E449" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F449" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" s="14" t="str">
+        <x:v>SRC126_013</x:v>
+      </x:c>
+      <x:c r="B450" s="14" t="str">
+        <x:v>Port of South Louisiana</x:v>
+      </x:c>
+      <x:c r="C450" s="14" t="str">
+        <x:v>Mississippi gateway</x:v>
+      </x:c>
+      <x:c r="D450" s="14" t="str">
+        <x:v>https://portsl.com/overview/</x:v>
+      </x:c>
+      <x:c r="E450" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F450" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" s="14" t="str">
+        <x:v>SRC126_014</x:v>
+      </x:c>
+      <x:c r="B451" s="14" t="str">
+        <x:v>U.S. Army Corps of Engineers</x:v>
+      </x:c>
+      <x:c r="C451" s="14" t="str">
+        <x:v>Mississippi navigation locks</x:v>
+      </x:c>
+      <x:c r="D451" s="14" t="str">
+        <x:v>https://www.usace.army.mil/Missions/Civil-Works/Navigation-Locks/</x:v>
+      </x:c>
+      <x:c r="E451" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F451" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" s="14" t="str">
+        <x:v>SRC126_015</x:v>
+      </x:c>
+      <x:c r="B452" s="14" t="str">
+        <x:v>Great Lakes St. Lawrence Seaway System</x:v>
+      </x:c>
+      <x:c r="C452" s="14" t="str">
+        <x:v>Locks / canals / channels</x:v>
+      </x:c>
+      <x:c r="D452" s="14" t="str">
+        <x:v>https://greatlakes-seaway.com/en/the-seaway/our-locks-and-channels/</x:v>
+      </x:c>
+      <x:c r="E452" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F452" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" s="14" t="str">
+        <x:v>SRC126_016</x:v>
+      </x:c>
+      <x:c r="B453" s="14" t="str">
+        <x:v>TEGRAM</x:v>
+      </x:c>
+      <x:c r="C453" s="14" t="str">
+        <x:v>TEGRAM consortium structure</x:v>
+      </x:c>
+      <x:c r="D453" s="14" t="str">
+        <x:v>https://tegram.com.br/sobre/</x:v>
+      </x:c>
+      <x:c r="E453" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F453" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" s="14" t="str">
+        <x:v>SRC126_017</x:v>
+      </x:c>
+      <x:c r="B454" s="14" t="str">
+        <x:v>Port of Itaqui</x:v>
+      </x:c>
+      <x:c r="C454" s="14" t="str">
+        <x:v>Itaqui authority / port context</x:v>
+      </x:c>
+      <x:c r="D454" s="14" t="str">
+        <x:v>https://www.portodoitaqui.com/</x:v>
+      </x:c>
+      <x:c r="E454" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F454" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" s="14" t="str">
+        <x:v>SRC126_018</x:v>
+      </x:c>
+      <x:c r="B455" s="14" t="str">
+        <x:v>Vancouver Fraser Port Authority</x:v>
+      </x:c>
+      <x:c r="C455" s="14" t="str">
+        <x:v>Port of Vancouver gateway reference</x:v>
+      </x:c>
+      <x:c r="D455" s="14" t="str">
+        <x:v>https://www.portvancouver.com/</x:v>
+      </x:c>
+      <x:c r="E455" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F455" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+      <x:c r="B456" s="14" t="str">
+        <x:v>PerGenova Breakwater Consortium</x:v>
+      </x:c>
+      <x:c r="C456" s="14" t="str">
+        <x:v>32nd caisson, crest wall, current project status and rail integration</x:v>
+      </x:c>
+      <x:c r="D456" s="14" t="str">
+        <x:v>https://www.pergenovadigaforanea.it/en/news/work-begins-on-crest-wall-of-new-genoa-breakwater-new-caisson-also-installed-offshore.html</x:v>
+      </x:c>
+      <x:c r="E456" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F456" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+      <x:c r="B457" s="14" t="str">
+        <x:v>Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+      <x:c r="C457" s="14" t="str">
+        <x:v>Breakwater design, access channel, turning basin and project scale</x:v>
+      </x:c>
+      <x:c r="D457" s="14" t="str">
+        <x:v>https://www.portsofgenoa.com/it/nuova-diga-foranea-di-genova/il-progetto.html</x:v>
+      </x:c>
+      <x:c r="E457" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F457" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+      <x:c r="B458" s="14" t="str">
+        <x:v>Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+      <x:c r="C458" s="14" t="str">
+        <x:v>PerGenova consortium members and Rhine-Alpine / Terzo Valico relationship</x:v>
+      </x:c>
+      <x:c r="D458" s="14" t="str">
+        <x:v>https://www.portsofgenoa.com/en/magazine/news/laying-first-stone-for-genoas-new-breakwater.html?format=pdf</x:v>
+      </x:c>
+      <x:c r="E458" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F458" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" s="14" t="str">
+        <x:v>SRC1261_004</x:v>
+      </x:c>
+      <x:c r="B459" s="14" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C459" s="14" t="str">
+        <x:v>Genoa megaship access expansion article</x:v>
+      </x:c>
+      <x:c r="D459" s="14" t="str">
+        <x:v>https://splash247.com/genoa-pushes-ahead-with-megaship-access-expansion/</x:v>
+      </x:c>
+      <x:c r="E459" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F459" s="14" t="str">
+        <x:v>Secondary / specialist maritime media</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R79c78b547e5a4f17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R5f979e33d1df4a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R7f5f674e18754420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rbdbcc2fa44224fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Re90232824ff3415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="Raf4e1deb52d0412a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9453,6 +9453,146 @@
         <x:v>Secondary / specialist maritime media</x:v>
       </x:c>
     </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="str">
+        <x:v>SRC130_001</x:v>
+      </x:c>
+      <x:c r="B460" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C460" t="str">
+        <x:v>LADY MARIIA sanctions record; IMO 9220641; Russia flag; roll-on/roll-off; linked to MG-FLOT LLC</x:v>
+      </x:c>
+      <x:c r="D460" t="str">
+        <x:v>https://sanctionssearch.ofac.treas.gov/Details.aspx?id=37089</x:v>
+      </x:c>
+      <x:c r="E460" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F460" t="str">
+        <x:v>Official / sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="str">
+        <x:v>SRC130_002</x:v>
+      </x:c>
+      <x:c r="B461" t="str">
+        <x:v>UK FCDO / UK Sanctions List</x:v>
+      </x:c>
+      <x:c r="C461" t="str">
+        <x:v>SUN IMO 9293117; owner/operator Wavewhisper Shipping Ltd; 2005 build; UK shipping sanctions</x:v>
+      </x:c>
+      <x:c r="D461" t="str">
+        <x:v>https://sanctionslist.fcdo.gov.uk/docs/UK-Sanctions-List.pdf</x:v>
+      </x:c>
+      <x:c r="E461" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F461" t="str">
+        <x:v>Official / sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="str">
+        <x:v>SRC130_003</x:v>
+      </x:c>
+      <x:c r="B462" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C462" t="str">
+        <x:v>ELOISE IMO 9233234; Gabon flag; 2002; linked to Vroom Marine Venture FZE</x:v>
+      </x:c>
+      <x:c r="D462" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20250430</x:v>
+      </x:c>
+      <x:c r="E462" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F462" t="str">
+        <x:v>Official / sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="str">
+        <x:v>SRC130_004</x:v>
+      </x:c>
+      <x:c r="B463" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C463" t="str">
+        <x:v>AL SAFA IMO 9222649; Panama flag; 2001; linked to Manarat Alkhaleej Marine Services FZE</x:v>
+      </x:c>
+      <x:c r="D463" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20260206</x:v>
+      </x:c>
+      <x:c r="E463" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F463" t="str">
+        <x:v>Official / sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="str">
+        <x:v>SRC130_005</x:v>
+      </x:c>
+      <x:c r="B464" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C464" t="str">
+        <x:v>ANSHUN II IMO 9253117; Panama flag; 2003; linked to Laurel Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="D464" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20260424</x:v>
+      </x:c>
+      <x:c r="E464" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F464" t="str">
+        <x:v>Official / sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="str">
+        <x:v>SRC130_006</x:v>
+      </x:c>
+      <x:c r="B465" t="str">
+        <x:v>Power &amp; Corridors</x:v>
+      </x:c>
+      <x:c r="C465" t="str">
+        <x:v>Lady Mariia central Mediterranean drone-attack alert, 7 Sep 2026</x:v>
+      </x:c>
+      <x:c r="D465" t="str">
+        <x:v>https://www.powerncorridors.com/maritime-alert-central-mediterranean-crete-libya-07-sept-2026/</x:v>
+      </x:c>
+      <x:c r="E465" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F465" t="str">
+        <x:v>P&amp;C intelligence / current incident</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="str">
+        <x:v>SRC130_007</x:v>
+      </x:c>
+      <x:c r="B466" t="str">
+        <x:v>USNI News</x:v>
+      </x:c>
+      <x:c r="C466" t="str">
+        <x:v>EUNAVFOR MED IRINI boarded SUN on 30 Aug 2026 for flag verification</x:v>
+      </x:c>
+      <x:c r="D466" t="str">
+        <x:v>https://news.usni.org/2026/09/02/european-union-naval-force-intercepts-suspected-russian-shadow-fleet-tanker</x:v>
+      </x:c>
+      <x:c r="E466" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F466" t="str">
+        <x:v>Major specialist reporting</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rbdbcc2fa44224fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Re90232824ff3415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="Raf4e1deb52d0412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rcfb9f4c13f044dbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rb9fc0420de6f4b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R3106c64d34f04eba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9593,6 +9593,246 @@
         <x:v>Major specialist reporting</x:v>
       </x:c>
     </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+      <x:c r="B467" t="str">
+        <x:v>U.S. Central Command</x:v>
+      </x:c>
+      <x:c r="C467" t="str">
+        <x:v>Sept. 8 strikes on RIESCO, HORIZON 1, KAVIZ, CHARMINAR and DERYA; crews warned; vessels rendered inoperable</x:v>
+      </x:c>
+      <x:c r="D467" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
+      </x:c>
+      <x:c r="E467" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F467" t="str">
+        <x:v>Official military / primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" t="str">
+        <x:v>SRC132_002</x:v>
+      </x:c>
+      <x:c r="B468" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C468" t="str">
+        <x:v>Sept. 8 five-tanker strike / escalation context</x:v>
+      </x:c>
+      <x:c r="D468" t="str">
+        <x:v>https://www.reuters.com/business/energy/us-military-says-it-destroyed-five-iranian-oil-carriers-after-attempted-missile-2026-09-08/</x:v>
+      </x:c>
+      <x:c r="E468" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F468" t="str">
+        <x:v>Major reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="B469" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C469" t="str">
+        <x:v>NEW ANDROS drone strike; Port Rashid listing vessel; UKMTO disabling-fire reports</x:v>
+      </x:c>
+      <x:c r="D469" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+      <x:c r="E469" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F469" t="str">
+        <x:v>Major reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" t="str">
+        <x:v>SRC132_004</x:v>
+      </x:c>
+      <x:c r="B470" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C470" t="str">
+        <x:v>DERYA IMO 9569700; NITC linkage; Iran sanctions</x:v>
+      </x:c>
+      <x:c r="D470" t="str">
+        <x:v>https://sanctionssearch.ofac.treas.gov/Details.aspx?id=25714</x:v>
+      </x:c>
+      <x:c r="E470" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F470" t="str">
+        <x:v>Official sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" t="str">
+        <x:v>SRC132_005</x:v>
+      </x:c>
+      <x:c r="B471" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C471" t="str">
+        <x:v>CHARMINAR IMO 9318022; IRAN-EO13902; linked to Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="D471" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20250730_33</x:v>
+      </x:c>
+      <x:c r="E471" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F471" t="str">
+        <x:v>Official sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" t="str">
+        <x:v>SRC132_006</x:v>
+      </x:c>
+      <x:c r="B472" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C472" t="str">
+        <x:v>AQUARIS / IMO 9251822 (now RIESCO); IRAN-EO13846; linked to Arkadia Maritime</x:v>
+      </x:c>
+      <x:c r="D472" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20251120</x:v>
+      </x:c>
+      <x:c r="E472" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F472" t="str">
+        <x:v>Official sanctions authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" t="str">
+        <x:v>SRC132_007</x:v>
+      </x:c>
+      <x:c r="B473" t="str">
+        <x:v>ClassNK</x:v>
+      </x:c>
+      <x:c r="C473" t="str">
+        <x:v>NEW ANDROS IMO 9294252; Panama flag; DWT 302,477; registered owner and management company</x:v>
+      </x:c>
+      <x:c r="D473" t="str">
+        <x:v>https://www.classnk.or.jp/register/regships/one_dsp.aspx?imo=9294252</x:v>
+      </x:c>
+      <x:c r="E473" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F473" t="str">
+        <x:v>Classification registry</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" t="str">
+        <x:v>SRC132_008</x:v>
+      </x:c>
+      <x:c r="B474" t="str">
+        <x:v>VesselFinder</x:v>
+      </x:c>
+      <x:c r="C474" t="str">
+        <x:v>RIESCO particulars: IMO 9251822; crude tanker; DWT 106,500; build 2003</x:v>
+      </x:c>
+      <x:c r="D474" t="str">
+        <x:v>https://www.vesselfinder.com/vessels/details/9251822</x:v>
+      </x:c>
+      <x:c r="E474" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F474" t="str">
+        <x:v>Vessel registry / AIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" t="str">
+        <x:v>SRC132_009</x:v>
+      </x:c>
+      <x:c r="B475" t="str">
+        <x:v>VesselFinder</x:v>
+      </x:c>
+      <x:c r="C475" t="str">
+        <x:v>HORIZON 1 particulars: IMO 9130456; LPG tanker; DWT 4,686; Palau</x:v>
+      </x:c>
+      <x:c r="D475" t="str">
+        <x:v>https://www.vesselfinder.com/vessels/details/9130456</x:v>
+      </x:c>
+      <x:c r="E475" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F475" t="str">
+        <x:v>Vessel registry / AIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" t="str">
+        <x:v>SRC132_010</x:v>
+      </x:c>
+      <x:c r="B476" t="str">
+        <x:v>VesselFinder</x:v>
+      </x:c>
+      <x:c r="C476" t="str">
+        <x:v>KAVIZ particulars: IMO 9282041; crude tanker; DWT 115,392</x:v>
+      </x:c>
+      <x:c r="D476" t="str">
+        <x:v>https://www.vesselfinder.com/vessels/details/9282041</x:v>
+      </x:c>
+      <x:c r="E476" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F476" t="str">
+        <x:v>Vessel registry / AIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" t="str">
+        <x:v>SRC132_011</x:v>
+      </x:c>
+      <x:c r="B477" t="str">
+        <x:v>VesselFinder</x:v>
+      </x:c>
+      <x:c r="C477" t="str">
+        <x:v>CHARMINAR particulars: IMO 9318022; chemical/oil products tanker; DWT 50,922; Comoros AIS flag</x:v>
+      </x:c>
+      <x:c r="D477" t="str">
+        <x:v>https://www.vesselfinder.com/vessels/details/9318022</x:v>
+      </x:c>
+      <x:c r="E477" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F477" t="str">
+        <x:v>Vessel registry / AIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" t="str">
+        <x:v>SRC132_012</x:v>
+      </x:c>
+      <x:c r="B478" t="str">
+        <x:v>UKMTO</x:v>
+      </x:c>
+      <x:c r="C478" t="str">
+        <x:v>Advisory 127-26: several merchant vessels exposed to disabling fire in Northern Arabian Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D478" t="str">
+        <x:v>https://www.ukmto.org/</x:v>
+      </x:c>
+      <x:c r="E478" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F478" t="str">
+        <x:v>Official maritime security</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rcfb9f4c13f044dbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rb9fc0420de6f4b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R3106c64d34f04eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rcc09cce18e674e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R7f22dccac2e24f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R67b66a47c8f84631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9833,6 +9833,226 @@
         <x:v>Official maritime security</x:v>
       </x:c>
     </x:row>
+    <x:row r="479">
+      <x:c r="A479" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="B479" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="C479" t="str">
+        <x:v>Peninsula confirms fatal Hercules Star incident at anchorage off Dubai; one crewmember missing; 7,998 DWT tanker chartered from Hercules Tanker Management.</x:v>
+      </x:c>
+      <x:c r="D479" t="str">
+        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+      </x:c>
+      <x:c r="E479" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F479" t="str">
+        <x:v>Trade press / company-confirmed casualty</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="B480" t="str">
+        <x:v>CBC News</x:v>
+      </x:c>
+      <x:c r="C480" t="str">
+        <x:v>Headline-level record: Nisg̱a'a and Tahltan Nations mark official opening of a Stewart, B.C. port as expansion plans take shape. Detailed ownership, capacity and terminal facts remain to be verified.</x:v>
+      </x:c>
+      <x:c r="D480" t="str">
+        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+      </x:c>
+      <x:c r="E480" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F480" t="str">
+        <x:v>News report / access-limited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="B481" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C481" t="str">
+        <x:v>Cruise operators expand private destinations; 12 Caribbean private destinations reported in 2024, with substantial Royal Caribbean, Carnival and Norwegian investment.</x:v>
+      </x:c>
+      <x:c r="D481" t="str">
+        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+      </x:c>
+      <x:c r="E481" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F481" t="str">
+        <x:v>News / sector analysis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" t="str">
+        <x:v>SRC133_004</x:v>
+      </x:c>
+      <x:c r="B482" t="str">
+        <x:v>Noatum Maritime</x:v>
+      </x:c>
+      <x:c r="C482" t="str">
+        <x:v>SAFEEN Surveyor acquisition and specifications: VS460 MKIII DP subsea service vessel, built 2014, 75.5 m, 6,300 DWT, 80T AHC crane and 60-person accommodation.</x:v>
+      </x:c>
+      <x:c r="D482" t="str">
+        <x:v>https://www.noatummaritime.com/news-media/safeen-offshore-expands-subsea-service-capabilities-with-acquisition-of-new-vessel.html</x:v>
+      </x:c>
+      <x:c r="E482" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F482" t="str">
+        <x:v>Official company release</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" t="str">
+        <x:v>SRC133_005</x:v>
+      </x:c>
+      <x:c r="B483" t="str">
+        <x:v>Ulstein Group</x:v>
+      </x:c>
+      <x:c r="C483" t="str">
+        <x:v>SAFEEN 3000 reference: DP2 heavy-lift and pipelay vessel with 3,000-tonne fixed crane and 2,200-tonne revolving capacity.</x:v>
+      </x:c>
+      <x:c r="D483" t="str">
+        <x:v>https://ulstein.com/references/safeen-3000</x:v>
+      </x:c>
+      <x:c r="E483" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F483" t="str">
+        <x:v>Builder / designer reference</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" t="str">
+        <x:v>SRC133_006</x:v>
+      </x:c>
+      <x:c r="B484" t="str">
+        <x:v>Damen</x:v>
+      </x:c>
+      <x:c r="C484" t="str">
+        <x:v>Bu Tinah RSD-E Tug 2513 introduced as the first fully electric tug in the Middle East and assigned to SAFEEN's Khalifa Port tug fleet.</x:v>
+      </x:c>
+      <x:c r="D484" t="str">
+        <x:v>https://www.damen.com/en/news/2024/05/damen-and-safeen-bring-first-electric-tug-to-middle-east</x:v>
+      </x:c>
+      <x:c r="E484" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F484" t="str">
+        <x:v>Builder release</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" t="str">
+        <x:v>SRC133_007</x:v>
+      </x:c>
+      <x:c r="B485" t="str">
+        <x:v>Royal Caribbean</x:v>
+      </x:c>
+      <x:c r="C485" t="str">
+        <x:v>Perfect Day at CocoCay destination reference.</x:v>
+      </x:c>
+      <x:c r="D485" t="str">
+        <x:v>https://www.royalcaribbean.com/cococay-cruises</x:v>
+      </x:c>
+      <x:c r="E485" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F485" t="str">
+        <x:v>Official operator page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" t="str">
+        <x:v>SRC133_008</x:v>
+      </x:c>
+      <x:c r="B486" t="str">
+        <x:v>Carnival Cruise Line</x:v>
+      </x:c>
+      <x:c r="C486" t="str">
+        <x:v>Celebration Key destination reference.</x:v>
+      </x:c>
+      <x:c r="D486" t="str">
+        <x:v>https://www.carnival.com/cruise-to/celebration-key-cruises</x:v>
+      </x:c>
+      <x:c r="E486" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F486" t="str">
+        <x:v>Official operator page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" t="str">
+        <x:v>SRC133_009</x:v>
+      </x:c>
+      <x:c r="B487" t="str">
+        <x:v>Norwegian Cruise Line</x:v>
+      </x:c>
+      <x:c r="C487" t="str">
+        <x:v>Great Stirrup Cay destination reference.</x:v>
+      </x:c>
+      <x:c r="D487" t="str">
+        <x:v>https://www.ncl.com/freestyle-cruise/great-stirrup-cay</x:v>
+      </x:c>
+      <x:c r="E487" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F487" t="str">
+        <x:v>Official operator page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" t="str">
+        <x:v>SRC133_010</x:v>
+      </x:c>
+      <x:c r="B488" t="str">
+        <x:v>Disney Cruise Line</x:v>
+      </x:c>
+      <x:c r="C488" t="str">
+        <x:v>Disney Castaway Cay destination reference.</x:v>
+      </x:c>
+      <x:c r="D488" t="str">
+        <x:v>https://disneycruise.disney.go.com/ports/castaway-cay/</x:v>
+      </x:c>
+      <x:c r="E488" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F488" t="str">
+        <x:v>Official operator page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" t="str">
+        <x:v>SRC133_011</x:v>
+      </x:c>
+      <x:c r="B489" t="str">
+        <x:v>MSC Cruises</x:v>
+      </x:c>
+      <x:c r="C489" t="str">
+        <x:v>Ocean Cay MSC Marine Reserve destination reference.</x:v>
+      </x:c>
+      <x:c r="D489" t="str">
+        <x:v>https://www.msccruises.com/our-cruises/destinations/caribbean-and-antilles/bahamas/ocean-cay-msc-marine-reserve</x:v>
+      </x:c>
+      <x:c r="E489" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F489" t="str">
+        <x:v>Official operator page</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rcc09cce18e674e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R7f22dccac2e24f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R67b66a47c8f84631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rf31f6111c6944c8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rfb3d15a37d9e4ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="Rbe6b5c796dc143bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10053,6 +10053,166 @@
         <x:v>Official operator page</x:v>
       </x:c>
     </x:row>
+    <x:row r="490">
+      <x:c r="A490" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+      <x:c r="B490" t="str">
+        <x:v>Strait of Hormuz Ship Monitor</x:v>
+      </x:c>
+      <x:c r="C490" t="str">
+        <x:v>Monthly AIS-derived Strait crossing statistics; current month is partial and wartime AIS disruption makes counts conservative lower bounds.</x:v>
+      </x:c>
+      <x:c r="D490" t="str">
+        <x:v>https://hormuz.data-tracking.net/stats</x:v>
+      </x:c>
+      <x:c r="E490" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F490" t="str">
+        <x:v>Public data / CC BY 4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="B491" t="str">
+        <x:v>Strait of Hormuz Ship Monitor</x:v>
+      </x:c>
+      <x:c r="C491" t="str">
+        <x:v>Free public JSON/CSV API documentation; 30-minute AIS polling, 90-day history and no API key.</x:v>
+      </x:c>
+      <x:c r="D491" t="str">
+        <x:v>https://hormuz.data-tracking.net/api-docs</x:v>
+      </x:c>
+      <x:c r="E491" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F491" t="str">
+        <x:v>Public API documentation / CC BY 4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="B492" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C492" t="str">
+        <x:v>Hunter Group says a counterparty owes USD 55 million amid a tanker-rate benchmark dispute.</x:v>
+      </x:c>
+      <x:c r="D492" t="str">
+        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+      </x:c>
+      <x:c r="E492" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F492" t="str">
+        <x:v>Trade press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" t="str">
+        <x:v>SRC134_004</x:v>
+      </x:c>
+      <x:c r="B493" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="C493" t="str">
+        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
+      </x:c>
+      <x:c r="D493" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+      <x:c r="E493" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F493" t="str">
+        <x:v>Official company release</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="B494" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C494" t="str">
+        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading fined USD 1.75 million over illegal oily-waste discharges from MSC SAMIRA III.</x:v>
+      </x:c>
+      <x:c r="D494" t="str">
+        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+      </x:c>
+      <x:c r="E494" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F494" t="str">
+        <x:v>Trade press / court reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="B495" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C495" t="str">
+        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="D495" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="E495" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F495" t="str">
+        <x:v>Trade press / government-programme reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" t="str">
+        <x:v>SRC134_007</x:v>
+      </x:c>
+      <x:c r="B496" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C496" t="str">
+        <x:v>Arctic LNG 2 seeks about USD 1 billion from Hanwha Ocean in a shipbuilding-contract dispute.</x:v>
+      </x:c>
+      <x:c r="D496" t="str">
+        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
+      </x:c>
+      <x:c r="E496" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F496" t="str">
+        <x:v>Trade press / Reuters syndication</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="B497" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C497" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
+      </x:c>
+      <x:c r="D497" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+      <x:c r="E497" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F497" t="str">
+        <x:v>News / legal and energy reporting</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10266,6 +10426,38 @@
         <x:v>Use source lineage.</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>FEED134_001</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Strait of Hormuz Ship Monitor API</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>https://hormuz.data-tracking.net/api/summary?hours=24</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Hormuz crossings; ships by zone; daily traffic; oil/gas export estimates</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Security; trade flow; energy; chokepoint</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Deduplicate by endpoint, UTC period and vessel/crossing identifier</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Public JSON/CSV API; no key; poll no faster than source's 30-minute AIS refresh; CC BY 4.0.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rf31f6111c6944c8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rfb3d15a37d9e4ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="Rbe6b5c796dc143bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re89330a8455e4398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rc6e9cfb3fe324906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R784cd0a818e54185"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7878,16 +7878,16 @@
         <x:v>SRC_0380</x:v>
       </x:c>
       <x:c r="B381" s="14" t="str">
-        <x:v>Etihad Rail</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="C381" s="14" t="str">
-        <x:v>UAE National Rail Network: 900 km Ghuwaifat-Fujairah; freight active across 11 terminals and four major ports.</x:v>
+        <x:v>Strategic investment in Suksawat Terminal, Thailand</x:v>
       </x:c>
       <x:c r="D381" s="14" t="str">
-        <x:v>https://corporate.etihadrail.ae/en</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-expands-to-thailand-terminal/</x:v>
       </x:c>
       <x:c r="E381" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F381" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7898,19 +7898,19 @@
         <x:v>SRC_0381</x:v>
       </x:c>
       <x:c r="B382" s="14" t="str">
-        <x:v>Etihad Rail</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C382" s="14" t="str">
-        <x:v>Network completion: 38 locomotives, 1,000+ wagons; Ruwais, ICAD, Khalifa, Dubai Industrial City, Jebel Ali, Al Ghail and Fujairah freight nodes.</x:v>
+        <x:v>Gulftainer enters Thailand with Suksawat terminal investment</x:v>
       </x:c>
       <x:c r="D382" s="14" t="str">
-        <x:v>https://corporate.etihadrail.ae/en/newsroom/press/his-highness-sheikh-mohammed-bin-rashid-vice-president-and-prime-minister-and-ruler-of-dubai-announces-the-completion-of-the-uae-national-rail-network</x:v>
+        <x:v>https://splash247.com/gulftainer-enters-thailand-with-suksawat-terminal-investment/</x:v>
       </x:c>
       <x:c r="E382" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F382" s="14" t="str">
-        <x:v>Official / primary</x:v>
+        <x:v>Secondary maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -7918,16 +7918,16 @@
         <x:v>SRC_0382</x:v>
       </x:c>
       <x:c r="B383" s="14" t="str">
-        <x:v>Hafeet Rail</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="C383" s="14" t="str">
-        <x:v>238 km UAE-Oman link from Sohar into UAE network; ETCS Level 2; freight up to 15,000 t or 276 TEU/trip.</x:v>
+        <x:v>Dedicated GT Lines UAE–Umm Qasr service</x:v>
       </x:c>
       <x:c r="D383" s="14" t="str">
-        <x:v>https://www.hafeetrail.com/</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-strengthens-iraq-trade-gateway/</x:v>
       </x:c>
       <x:c r="E383" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F383" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7938,16 +7938,16 @@
         <x:v>SRC_0383</x:v>
       </x:c>
       <x:c r="B384" s="14" t="str">
-        <x:v>Etihad Rail / Hafeet Rail</x:v>
+        <x:v>AD Ports Group</x:v>
       </x:c>
       <x:c r="C384" s="14" t="str">
-        <x:v>Hafeet Rail 40% complete on 20 Apr 2026; JV of Etihad Rail, Oman Rail and Mubadala Investment.</x:v>
+        <x:v>Q1 2026 earnings presentation and CapEx disclosure</x:v>
       </x:c>
       <x:c r="D384" s="14" t="str">
-        <x:v>https://corporate.etihadrail.ae/en/newsroom/press/hafeet-rail-announces-40-completion-of-omanuae-railway-connection-project</x:v>
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/2026/documents/adpg-earnings-presentation-q1-2026.pdf</x:v>
       </x:c>
       <x:c r="E384" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F384" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7958,16 +7958,16 @@
         <x:v>SRC_0384</x:v>
       </x:c>
       <x:c r="B385" s="14" t="str">
-        <x:v>Saudi Arabia Railways</x:v>
+        <x:v>AD Ports Group</x:v>
       </x:c>
       <x:c r="C385" s="14" t="str">
-        <x:v>East Freight: 566 km King Abdulaziz Port Dammam-Riyadh; 2,596 freight cars.</x:v>
+        <x:v>Q2 2026 results and financial KPIs</x:v>
       </x:c>
       <x:c r="D385" s="14" t="str">
-        <x:v>https://sar.com.sa/about-sar/railnetwork/</x:v>
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
       </x:c>
       <x:c r="E385" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F385" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7978,16 +7978,16 @@
         <x:v>SRC_0385</x:v>
       </x:c>
       <x:c r="B386" s="14" t="str">
-        <x:v>Saudi Arabia Railways</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="C386" s="14" t="str">
-        <x:v>SAR wholly owned by PIF and sole owner/operator of Saudi intercity rail infrastructure.</x:v>
+        <x:v>FY2025 results and 2026 CapEx budget</x:v>
       </x:c>
       <x:c r="D386" s="14" t="str">
-        <x:v>https://www.sar.com.sa/about-sar/</x:v>
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
       </x:c>
       <x:c r="E386" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F386" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7998,16 +7998,16 @@
         <x:v>SRC_0386</x:v>
       </x:c>
       <x:c r="B387" s="14" t="str">
-        <x:v>Azerbaijan Transport Ministry</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="C387" s="14" t="str">
-        <x:v>Middle Corridor: 4,256 km rail + 508 km sea; China-Kazakhstan-Azerbaijan-Georgia, onward via BTK/Black Sea.</x:v>
+        <x:v>US$100m additional logistics investment in Dominican Republic</x:v>
       </x:c>
       <x:c r="D387" s="14" t="str">
-        <x:v>https://transit.gov.az/en/corridors/east-west-corridor</x:v>
+        <x:v>https://www.dpworld.com/en/news/usa/05262026_dp-world-to-expand-logistics-capacity-in-the-dr</x:v>
       </x:c>
       <x:c r="E387" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F387" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8018,16 +8018,16 @@
         <x:v>SRC_0387</x:v>
       </x:c>
       <x:c r="B388" s="14" t="str">
-        <x:v>Georgian Railway</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="C388" s="14" t="str">
-        <x:v>BTK route update, 2 Jun 2026.</x:v>
+        <x:v>£60m Southampton quay crane investment</x:v>
       </x:c>
       <x:c r="D388" s="14" t="str">
-        <x:v>https://www.railway.ge/baqo-tbilisi-yarsis-marshruti-akhal-shesadzleblobebs-qmnis/</x:v>
+        <x:v>https://www.dpworld.com/en/news/europes-largest-quay-cranes-arrive-at-dp-world-southampton</x:v>
       </x:c>
       <x:c r="E388" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F388" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8038,16 +8038,16 @@
         <x:v>SRC_0388</x:v>
       </x:c>
       <x:c r="B389" s="14" t="str">
-        <x:v>Georgian Railway</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="C389" s="14" t="str">
-        <x:v>Current schedule confirms Tbilisi-Poti and Tbilisi-Batumi corridors.</x:v>
+        <x:v>€48m initial Antwerp cold-chain hub investment</x:v>
       </x:c>
       <x:c r="D389" s="14" t="str">
-        <x:v>https://www.railway.ge/en/traffic-general-schedule/</x:v>
+        <x:v>https://www.dpworld.com/en/news/dp-world-expands-cold-chain-capabilities-with-new-48m-antwerp-hub</x:v>
       </x:c>
       <x:c r="E389" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F389" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8058,16 +8058,16 @@
         <x:v>SRC_0389</x:v>
       </x:c>
       <x:c r="B390" s="14" t="str">
-        <x:v>CN</x:v>
+        <x:v>DP World</x:v>
       </x:c>
       <x:c r="C390" s="14" t="str">
-        <x:v>CN rail network ~20,000 route-miles / 30,000 km, three coasts.</x:v>
+        <x:v>CAD13.3m Fraser Surrey rail-capacity investment</x:v>
       </x:c>
       <x:c r="D390" s="14" t="str">
-        <x:v>https://www.cn.ca/en/our-services/rail</x:v>
+        <x:v>https://www.dpworld.com/en/news/usa/rail-yard-expansion-fraser-surrey-terminal</x:v>
       </x:c>
       <x:c r="E390" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F390" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8078,16 +8078,16 @@
         <x:v>SRC_0390</x:v>
       </x:c>
       <x:c r="B391" s="14" t="str">
-        <x:v>CN</x:v>
+        <x:v>Siamgas and Petrochemicals</x:v>
       </x:c>
       <x:c r="C391" s="14" t="str">
-        <x:v>CN port network: Prince Rupert, Vancouver, Montreal, Halifax, New Orleans, Mobile and others.</x:v>
+        <x:v>Suksawat Terminal listed within current terminal and depot network</x:v>
       </x:c>
       <x:c r="D391" s="14" t="str">
-        <x:v>https://www.cn.ca/en/our-services/maps-and-network/ports</x:v>
+        <x:v>https://www.siamgas.com/products-services/</x:v>
       </x:c>
       <x:c r="E391" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F391" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8098,16 +8098,16 @@
         <x:v>SRC_0391</x:v>
       </x:c>
       <x:c r="B392" s="14" t="str">
-        <x:v>CPKC</x:v>
+        <x:v>Siamgas and Petrochemicals</x:v>
       </x:c>
       <x:c r="C392" s="14" t="str">
-        <x:v>CPKC port access includes Vancouver, Saint John and Lázaro Cárdenas.</x:v>
+        <x:v>Company profile and regional energy/logistics footprint</x:v>
       </x:c>
       <x:c r="D392" s="14" t="str">
-        <x:v>https://author.cpkcr.com/en/our-advantage/port-access</x:v>
+        <x:v>https://www.siamgas.com/about-us/</x:v>
       </x:c>
       <x:c r="E392" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F392" s="14" t="str">
         <x:v>Official / primary</x:v>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re89330a8455e4398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rc6e9cfb3fe324906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R784cd0a818e54185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R1749774f3e28467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R15d88add023441c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R4e85c9493e764e40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10213,6 +10213,146 @@
         <x:v>News / legal and energy reporting</x:v>
       </x:c>
     </x:row>
+    <x:row r="498">
+      <x:c r="A498" s="14" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="B498" s="14" t="str">
+        <x:v>Power &amp; Corridors</x:v>
+      </x:c>
+      <x:c r="C498" s="14" t="str">
+        <x:v>PGSA blacklist reference, vessel identities, list expansion and STS exposure</x:v>
+      </x:c>
+      <x:c r="D498" s="14" t="str">
+        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
+      </x:c>
+      <x:c r="E498" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F498" s="14" t="str">
+        <x:v>P&amp;C analysis / curated source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" s="14" t="str">
+        <x:v>SRC_JCG</x:v>
+      </x:c>
+      <x:c r="B499" s="14" t="str">
+        <x:v>Japan Coast Guard</x:v>
+      </x:c>
+      <x:c r="C499" s="14" t="str">
+        <x:v>Official Japan Coast Guard press releases, foreign-vessel rescue updates and navigational information</x:v>
+      </x:c>
+      <x:c r="D499" s="14" t="str">
+        <x:v>https://www.kaiho.mlit.go.jp/e/topics_archive/index.html</x:v>
+      </x:c>
+      <x:c r="E499" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F499" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" s="14" t="str">
+        <x:v>SRC_KCG</x:v>
+      </x:c>
+      <x:c r="B500" s="14" t="str">
+        <x:v>Korea Coast Guard</x:v>
+      </x:c>
+      <x:c r="C500" s="14" t="str">
+        <x:v>Official Korea Coast Guard national/regional press releases and maritime incident reporting</x:v>
+      </x:c>
+      <x:c r="D500" s="14" t="str">
+        <x:v>https://www.kcg.go.kr/</x:v>
+      </x:c>
+      <x:c r="E500" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F500" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" s="14" t="str">
+        <x:v>SRC_ICG</x:v>
+      </x:c>
+      <x:c r="B501" s="14" t="str">
+        <x:v>Indian Coast Guard</x:v>
+      </x:c>
+      <x:c r="C501" s="14" t="str">
+        <x:v>Official Indian Coast Guard news, SAR, pollution response and maritime assistance</x:v>
+      </x:c>
+      <x:c r="D501" s="14" t="str">
+        <x:v>https://indiancoastguard.gov.in/</x:v>
+      </x:c>
+      <x:c r="E501" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F501" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" s="14" t="str">
+        <x:v>SRC_DGS_INDIA</x:v>
+      </x:c>
+      <x:c r="B502" s="14" t="str">
+        <x:v>Directorate General of Shipping India</x:v>
+      </x:c>
+      <x:c r="C502" s="14" t="str">
+        <x:v>Official casualty investigation circulars and marine safety guidance</x:v>
+      </x:c>
+      <x:c r="D502" s="14" t="str">
+        <x:v>https://www.dgshipping.gov.in/</x:v>
+      </x:c>
+      <x:c r="E502" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F502" s="14" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503" s="14" t="str">
+        <x:v>SRC_SEC_GASLOG</x:v>
+      </x:c>
+      <x:c r="B503" s="14" t="str">
+        <x:v>Public vessel-reference sources</x:v>
+      </x:c>
+      <x:c r="C503" s="14" t="str">
+        <x:v>GasLog Shanghai identity/ownership sample used to test canonical vessel enrichment</x:v>
+      </x:c>
+      <x:c r="D503" s="14" t="str">
+        <x:v>https://www.shipspotting.com/photos/3877208</x:v>
+      </x:c>
+      <x:c r="E503" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F503" s="14" t="str">
+        <x:v>Secondary vessel-reference source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" s="14" t="str">
+        <x:v>SRC_SEC_ALREK</x:v>
+      </x:c>
+      <x:c r="B504" s="14" t="str">
+        <x:v>Public vessel-reference sources</x:v>
+      </x:c>
+      <x:c r="C504" s="14" t="str">
+        <x:v>Al Rekayyat identity/ownership sample used to test canonical vessel enrichment</x:v>
+      </x:c>
+      <x:c r="D504" s="14" t="str">
+        <x:v>https://www.ship-db.de/nawbn.php?wbn_nr=hyhu1910010E</x:v>
+      </x:c>
+      <x:c r="E504" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F504" s="14" t="str">
+        <x:v>Secondary vessel-reference source</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10458,6 +10598,198 @@
         <x:v>Public JSON/CSV API; no key; poll no faster than source's 30-minute AIS refresh; CC BY 4.0.</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>FEED_SEC_001</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>Japan Coast Guard – Press Releases</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>https://www.kaiho.mlit.go.jp/e/topics_archive/index.html</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Japan / surrounding waters</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>Maritime casualty; SAR; navigation warning; pollution; enforcement</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>Deduplicate by date + vessel/incident + official update number</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>Primary MARSEC monitoring feed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>FEED_SEC_002</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>Japan Coast Guard – Foreign Vessel Rescue</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>https://www.kaiho.mlit.go.jp/info/topics/rescueforeignvessels.html</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Japan / high seas around Japan</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>SAR; crew injury; missing person; distressed vessel</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>Resolve vessel by IMO/name before canonical event creation</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>Useful structured foreign-vessel incident index.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>FEED_SEC_003</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>Korea Coast Guard – Press Releases</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>https://www.kcg.go.kr/</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>South Korea / Korean waters</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>Grounding; collision; SAR; pollution; enforcement; maritime security</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>Deduplicate national/regional reposts by incident/date/location</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>Regional stations often publish incident detail first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>FEED_SEC_004</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>Indian Coast Guard – News &amp; Assistance</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>https://indiancoastguard.gov.in/</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>India / Indian EEZ</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>SAR; vessel fire; grounding; pollution; maritime security; response</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>Resolve official incident to vessel/IMO and MRCC/region</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>Primary Indian MARSEC operational source.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>FEED_SEC_005</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>DG Shipping India – Casualty / Safety</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>https://www.dgshipping.gov.in/</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>India / Indian shipping</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>Marine casualty; casualty investigation; safety circular; regulatory response</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>Separate casualty occurrence from later safety circular/investigation</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>Primary regulatory/casualty source.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>FEED_SEC_006</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>PGSA Compliance Monitor</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>Strait of Hormuz / Gulf / Oman approaches</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>Compliance restriction; designation; STS exposure; enforcement; delisting</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>IMO-first; do not merge PGSA with OFAC/EU/UK legal sanctions</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>P&amp;C curated monitor pending primary PGSA machine-readable source.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R1749774f3e28467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R15d88add023441c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R4e85c9493e764e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re80f78c2bf5146ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rf10aef9e4d06453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R6ab768ad7c664d99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7878,16 +7878,16 @@
         <x:v>SRC_0380</x:v>
       </x:c>
       <x:c r="B381" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>Etihad Rail</x:v>
       </x:c>
       <x:c r="C381" s="14" t="str">
-        <x:v>Strategic investment in Suksawat Terminal, Thailand</x:v>
+        <x:v>UAE National Rail Network: 900 km Ghuwaifat-Fujairah; freight active across 11 terminals and four major ports.</x:v>
       </x:c>
       <x:c r="D381" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-expands-to-thailand-terminal/</x:v>
+        <x:v>https://corporate.etihadrail.ae/en</x:v>
       </x:c>
       <x:c r="E381" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F381" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7898,19 +7898,19 @@
         <x:v>SRC_0381</x:v>
       </x:c>
       <x:c r="B382" s="14" t="str">
-        <x:v>Splash247</x:v>
+        <x:v>Etihad Rail</x:v>
       </x:c>
       <x:c r="C382" s="14" t="str">
-        <x:v>Gulftainer enters Thailand with Suksawat terminal investment</x:v>
+        <x:v>Network completion: 38 locomotives, 1,000+ wagons; Ruwais, ICAD, Khalifa, Dubai Industrial City, Jebel Ali, Al Ghail and Fujairah freight nodes.</x:v>
       </x:c>
       <x:c r="D382" s="14" t="str">
-        <x:v>https://splash247.com/gulftainer-enters-thailand-with-suksawat-terminal-investment/</x:v>
+        <x:v>https://corporate.etihadrail.ae/en/newsroom/press/his-highness-sheikh-mohammed-bin-rashid-vice-president-and-prime-minister-and-ruler-of-dubai-announces-the-completion-of-the-uae-national-rail-network</x:v>
       </x:c>
       <x:c r="E382" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F382" s="14" t="str">
-        <x:v>Secondary maritime media</x:v>
+        <x:v>Official / primary</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -7918,16 +7918,16 @@
         <x:v>SRC_0382</x:v>
       </x:c>
       <x:c r="B383" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>Hafeet Rail</x:v>
       </x:c>
       <x:c r="C383" s="14" t="str">
-        <x:v>Dedicated GT Lines UAE–Umm Qasr service</x:v>
+        <x:v>238 km UAE-Oman link from Sohar into UAE network; ETCS Level 2; freight up to 15,000 t or 276 TEU/trip.</x:v>
       </x:c>
       <x:c r="D383" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-strengthens-iraq-trade-gateway/</x:v>
+        <x:v>https://www.hafeetrail.com/</x:v>
       </x:c>
       <x:c r="E383" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F383" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7938,16 +7938,16 @@
         <x:v>SRC_0383</x:v>
       </x:c>
       <x:c r="B384" s="14" t="str">
-        <x:v>AD Ports Group</x:v>
+        <x:v>Etihad Rail / Hafeet Rail</x:v>
       </x:c>
       <x:c r="C384" s="14" t="str">
-        <x:v>Q1 2026 earnings presentation and CapEx disclosure</x:v>
+        <x:v>Hafeet Rail 40% complete on 20 Apr 2026; JV of Etihad Rail, Oman Rail and Mubadala Investment.</x:v>
       </x:c>
       <x:c r="D384" s="14" t="str">
-        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/2026/documents/adpg-earnings-presentation-q1-2026.pdf</x:v>
+        <x:v>https://corporate.etihadrail.ae/en/newsroom/press/hafeet-rail-announces-40-completion-of-omanuae-railway-connection-project</x:v>
       </x:c>
       <x:c r="E384" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F384" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7958,16 +7958,16 @@
         <x:v>SRC_0384</x:v>
       </x:c>
       <x:c r="B385" s="14" t="str">
-        <x:v>AD Ports Group</x:v>
+        <x:v>Saudi Arabia Railways</x:v>
       </x:c>
       <x:c r="C385" s="14" t="str">
-        <x:v>Q2 2026 results and financial KPIs</x:v>
+        <x:v>East Freight: 566 km King Abdulaziz Port Dammam-Riyadh; 2,596 freight cars.</x:v>
       </x:c>
       <x:c r="D385" s="14" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+        <x:v>https://sar.com.sa/about-sar/railnetwork/</x:v>
       </x:c>
       <x:c r="E385" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F385" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7978,16 +7978,16 @@
         <x:v>SRC_0385</x:v>
       </x:c>
       <x:c r="B386" s="14" t="str">
-        <x:v>DP World</x:v>
+        <x:v>Saudi Arabia Railways</x:v>
       </x:c>
       <x:c r="C386" s="14" t="str">
-        <x:v>FY2025 results and 2026 CapEx budget</x:v>
+        <x:v>SAR wholly owned by PIF and sole owner/operator of Saudi intercity rail infrastructure.</x:v>
       </x:c>
       <x:c r="D386" s="14" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+        <x:v>https://www.sar.com.sa/about-sar/</x:v>
       </x:c>
       <x:c r="E386" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F386" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -7998,16 +7998,16 @@
         <x:v>SRC_0386</x:v>
       </x:c>
       <x:c r="B387" s="14" t="str">
-        <x:v>DP World</x:v>
+        <x:v>Azerbaijan Transport Ministry</x:v>
       </x:c>
       <x:c r="C387" s="14" t="str">
-        <x:v>US$100m additional logistics investment in Dominican Republic</x:v>
+        <x:v>Middle Corridor: 4,256 km rail + 508 km sea; China-Kazakhstan-Azerbaijan-Georgia, onward via BTK/Black Sea.</x:v>
       </x:c>
       <x:c r="D387" s="14" t="str">
-        <x:v>https://www.dpworld.com/en/news/usa/05262026_dp-world-to-expand-logistics-capacity-in-the-dr</x:v>
+        <x:v>https://transit.gov.az/en/corridors/east-west-corridor</x:v>
       </x:c>
       <x:c r="E387" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F387" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8018,16 +8018,16 @@
         <x:v>SRC_0387</x:v>
       </x:c>
       <x:c r="B388" s="14" t="str">
-        <x:v>DP World</x:v>
+        <x:v>Georgian Railway</x:v>
       </x:c>
       <x:c r="C388" s="14" t="str">
-        <x:v>£60m Southampton quay crane investment</x:v>
+        <x:v>BTK route update, 2 Jun 2026.</x:v>
       </x:c>
       <x:c r="D388" s="14" t="str">
-        <x:v>https://www.dpworld.com/en/news/europes-largest-quay-cranes-arrive-at-dp-world-southampton</x:v>
+        <x:v>https://www.railway.ge/baqo-tbilisi-yarsis-marshruti-akhal-shesadzleblobebs-qmnis/</x:v>
       </x:c>
       <x:c r="E388" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F388" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8038,16 +8038,16 @@
         <x:v>SRC_0388</x:v>
       </x:c>
       <x:c r="B389" s="14" t="str">
-        <x:v>DP World</x:v>
+        <x:v>Georgian Railway</x:v>
       </x:c>
       <x:c r="C389" s="14" t="str">
-        <x:v>€48m initial Antwerp cold-chain hub investment</x:v>
+        <x:v>Current schedule confirms Tbilisi-Poti and Tbilisi-Batumi corridors.</x:v>
       </x:c>
       <x:c r="D389" s="14" t="str">
-        <x:v>https://www.dpworld.com/en/news/dp-world-expands-cold-chain-capabilities-with-new-48m-antwerp-hub</x:v>
+        <x:v>https://www.railway.ge/en/traffic-general-schedule/</x:v>
       </x:c>
       <x:c r="E389" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F389" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8058,16 +8058,16 @@
         <x:v>SRC_0389</x:v>
       </x:c>
       <x:c r="B390" s="14" t="str">
-        <x:v>DP World</x:v>
+        <x:v>CN</x:v>
       </x:c>
       <x:c r="C390" s="14" t="str">
-        <x:v>CAD13.3m Fraser Surrey rail-capacity investment</x:v>
+        <x:v>CN rail network ~20,000 route-miles / 30,000 km, three coasts.</x:v>
       </x:c>
       <x:c r="D390" s="14" t="str">
-        <x:v>https://www.dpworld.com/en/news/usa/rail-yard-expansion-fraser-surrey-terminal</x:v>
+        <x:v>https://www.cn.ca/en/our-services/rail</x:v>
       </x:c>
       <x:c r="E390" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F390" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8078,16 +8078,16 @@
         <x:v>SRC_0390</x:v>
       </x:c>
       <x:c r="B391" s="14" t="str">
-        <x:v>Siamgas and Petrochemicals</x:v>
+        <x:v>CN</x:v>
       </x:c>
       <x:c r="C391" s="14" t="str">
-        <x:v>Suksawat Terminal listed within current terminal and depot network</x:v>
+        <x:v>CN port network: Prince Rupert, Vancouver, Montreal, Halifax, New Orleans, Mobile and others.</x:v>
       </x:c>
       <x:c r="D391" s="14" t="str">
-        <x:v>https://www.siamgas.com/products-services/</x:v>
+        <x:v>https://www.cn.ca/en/our-services/maps-and-network/ports</x:v>
       </x:c>
       <x:c r="E391" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F391" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -8098,16 +8098,16 @@
         <x:v>SRC_0391</x:v>
       </x:c>
       <x:c r="B392" s="14" t="str">
-        <x:v>Siamgas and Petrochemicals</x:v>
+        <x:v>CPKC</x:v>
       </x:c>
       <x:c r="C392" s="14" t="str">
-        <x:v>Company profile and regional energy/logistics footprint</x:v>
+        <x:v>CPKC port access includes Vancouver, Saint John and Lázaro Cárdenas.</x:v>
       </x:c>
       <x:c r="D392" s="14" t="str">
-        <x:v>https://www.siamgas.com/about-us/</x:v>
+        <x:v>https://author.cpkcr.com/en/our-advantage/port-access</x:v>
       </x:c>
       <x:c r="E392" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="F392" s="14" t="str">
         <x:v>Official / primary</x:v>
@@ -9835,522 +9835,542 @@
     </x:row>
     <x:row r="479">
       <x:c r="A479" t="str">
-        <x:v>SRC133_001</x:v>
+        <x:v>SRC260910_001</x:v>
       </x:c>
       <x:c r="B479" t="str">
-        <x:v>Ship &amp; Bunker</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C479" t="str">
-        <x:v>Peninsula confirms fatal Hercules Star incident at anchorage off Dubai; one crewmember missing; 7,998 DWT tanker chartered from Hercules Tanker Management.</x:v>
+        <x:v>Houthi Forces Attack Saudi Aramco's Jazan Refinery</x:v>
       </x:c>
       <x:c r="D479" t="str">
-        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+        <x:v>https://maritime-executive.com/article/houthi-forces-attack-saudi-aramco-s-jazan-refinery</x:v>
       </x:c>
       <x:c r="E479" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F479" t="str">
-        <x:v>Trade press / company-confirmed casualty</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
       <x:c r="A480" t="str">
-        <x:v>SRC133_002</x:v>
+        <x:v>SRC260910_002</x:v>
       </x:c>
       <x:c r="B480" t="str">
-        <x:v>CBC News</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C480" t="str">
-        <x:v>Headline-level record: Nisg̱a'a and Tahltan Nations mark official opening of a Stewart, B.C. port as expansion plans take shape. Detailed ownership, capacity and terminal facts remain to be verified.</x:v>
+        <x:v>U.S. Forces Destroy Drug-Runners' Floating Gas Station Off Ecuador</x:v>
       </x:c>
       <x:c r="D480" t="str">
-        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-forces-destroy-drug-runners-floating-gas-station-off-ecuador</x:v>
       </x:c>
       <x:c r="E480" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F480" t="str">
-        <x:v>News report / access-limited</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
       <x:c r="A481" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_003</x:v>
       </x:c>
       <x:c r="B481" t="str">
-        <x:v>Reuters</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C481" t="str">
-        <x:v>Cruise operators expand private destinations; 12 Caribbean private destinations reported in 2024, with substantial Royal Caribbean, Carnival and Norwegian investment.</x:v>
+        <x:v>Cochin and Drydocks World seal Kochi repair venture</x:v>
       </x:c>
       <x:c r="D481" t="str">
-        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+        <x:v>https://splash247.com/cochin-and-drydocks-world-seal-kochi-repair-venture/</x:v>
       </x:c>
       <x:c r="E481" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F481" t="str">
-        <x:v>News / sector analysis</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
       <x:c r="A482" t="str">
-        <x:v>SRC133_004</x:v>
+        <x:v>SRC260910_004</x:v>
       </x:c>
       <x:c r="B482" t="str">
-        <x:v>Noatum Maritime</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C482" t="str">
-        <x:v>SAFEEN Surveyor acquisition and specifications: VS460 MKIII DP subsea service vessel, built 2014, 75.5 m, 6,300 DWT, 80T AHC crane and 60-person accommodation.</x:v>
+        <x:v>U.S. Hits Five More Iranian Tankers After Second Attack on U.S. Warship</x:v>
       </x:c>
       <x:c r="D482" t="str">
-        <x:v>https://www.noatummaritime.com/news-media/safeen-offshore-expands-subsea-service-capabilities-with-acquisition-of-new-vessel.html</x:v>
+        <x:v>https://maritime-executive.com/article/u-s-hits-three-more-iranian-tankers-after-second-attack-on-u-s-warship</x:v>
       </x:c>
       <x:c r="E482" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F482" t="str">
-        <x:v>Official company release</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
       <x:c r="A483" t="str">
-        <x:v>SRC133_005</x:v>
+        <x:v>SRC260910_005</x:v>
       </x:c>
       <x:c r="B483" t="str">
-        <x:v>Ulstein Group</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C483" t="str">
-        <x:v>SAFEEN 3000 reference: DP2 heavy-lift and pipelay vessel with 3,000-tonne fixed crane and 2,200-tonne revolving capacity.</x:v>
+        <x:v>HMM Continues Diversification with $3.5B Ore Deal with Vale</x:v>
       </x:c>
       <x:c r="D483" t="str">
-        <x:v>https://ulstein.com/references/safeen-3000</x:v>
+        <x:v>https://maritime-executive.com/article/hmm-continues-diversification-with-3-5b-ore-deal-with-vale</x:v>
       </x:c>
       <x:c r="E483" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F483" t="str">
-        <x:v>Builder / designer reference</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
       <x:c r="A484" t="str">
-        <x:v>SRC133_006</x:v>
+        <x:v>SRC260910_006</x:v>
       </x:c>
       <x:c r="B484" t="str">
-        <x:v>Damen</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C484" t="str">
-        <x:v>Bu Tinah RSD-E Tug 2513 introduced as the first fully electric tug in the Middle East and assigned to SAFEEN's Khalifa Port tug fleet.</x:v>
+        <x:v>Iran Battles to Beat the Blockade</x:v>
       </x:c>
       <x:c r="D484" t="str">
-        <x:v>https://www.damen.com/en/news/2024/05/damen-and-safeen-bring-first-electric-tug-to-middle-east</x:v>
+        <x:v>https://maritime-executive.com/editorials/iran-battles-to-beat-the-blockade</x:v>
       </x:c>
       <x:c r="E484" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F484" t="str">
-        <x:v>Builder release</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
       <x:c r="A485" t="str">
-        <x:v>SRC133_007</x:v>
+        <x:v>SRC260910_007</x:v>
       </x:c>
       <x:c r="B485" t="str">
-        <x:v>Royal Caribbean</x:v>
+        <x:v>The Maritime Executive</x:v>
       </x:c>
       <x:c r="C485" t="str">
-        <x:v>Perfect Day at CocoCay destination reference.</x:v>
+        <x:v>US Investors Top Hanwha's Bid for Austal USA</x:v>
       </x:c>
       <x:c r="D485" t="str">
-        <x:v>https://www.royalcaribbean.com/cococay-cruises</x:v>
+        <x:v>https://maritime-executive.com/article/us-investors-top-hanwha-s-bid-for-austal-usa</x:v>
       </x:c>
       <x:c r="E485" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F485" t="str">
-        <x:v>Official operator page</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
       <x:c r="A486" t="str">
-        <x:v>SRC133_008</x:v>
+        <x:v>SRC260910_008</x:v>
       </x:c>
       <x:c r="B486" t="str">
-        <x:v>Carnival Cruise Line</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C486" t="str">
-        <x:v>Celebration Key destination reference.</x:v>
+        <x:v>Simandou's Morebaya port moves into commissioning</x:v>
       </x:c>
       <x:c r="D486" t="str">
-        <x:v>https://www.carnival.com/cruise-to/celebration-key-cruises</x:v>
+        <x:v>https://splash247.com/simandous-morebaya-port-moves-into-commissioning/</x:v>
       </x:c>
       <x:c r="E486" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F486" t="str">
-        <x:v>Official operator page</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
       <x:c r="A487" t="str">
-        <x:v>SRC133_009</x:v>
+        <x:v>SRC260910_009</x:v>
       </x:c>
       <x:c r="B487" t="str">
-        <x:v>Norwegian Cruise Line</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C487" t="str">
-        <x:v>Great Stirrup Cay destination reference.</x:v>
+        <x:v>Thailand's Songkhla gets first ship-to-shore cranes</x:v>
       </x:c>
       <x:c r="D487" t="str">
-        <x:v>https://www.ncl.com/freestyle-cruise/great-stirrup-cay</x:v>
+        <x:v>https://splash247.com/thailands-songkhla-gets-first-ship-to-shore-cranes/</x:v>
       </x:c>
       <x:c r="E487" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F487" t="str">
-        <x:v>Official operator page</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
       <x:c r="A488" t="str">
-        <x:v>SRC133_010</x:v>
+        <x:v>SRC260910_010</x:v>
       </x:c>
       <x:c r="B488" t="str">
-        <x:v>Disney Cruise Line</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C488" t="str">
-        <x:v>Disney Castaway Cay destination reference.</x:v>
+        <x:v>Ningbo clears $223m offshore wind port development</x:v>
       </x:c>
       <x:c r="D488" t="str">
-        <x:v>https://disneycruise.disney.go.com/ports/castaway-cay/</x:v>
+        <x:v>https://splash247.com/ningbo-clears-223m-offshore-wind-port-development/</x:v>
       </x:c>
       <x:c r="E488" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F488" t="str">
-        <x:v>Official operator page</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
       <x:c r="A489" t="str">
-        <x:v>SRC133_011</x:v>
+        <x:v>SRC260910_011</x:v>
       </x:c>
       <x:c r="B489" t="str">
-        <x:v>MSC Cruises</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C489" t="str">
-        <x:v>Ocean Cay MSC Marine Reserve destination reference.</x:v>
+        <x:v>US lines up $15m for Colombo port digital upgrade</x:v>
       </x:c>
       <x:c r="D489" t="str">
-        <x:v>https://www.msccruises.com/our-cruises/destinations/caribbean-and-antilles/bahamas/ocean-cay-msc-marine-reserve</x:v>
+        <x:v>https://splash247.com/us-lines-up-15m-for-colombo-port-digital-upgrade/</x:v>
       </x:c>
       <x:c r="E489" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F489" t="str">
-        <x:v>Official operator page</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
       <x:c r="A490" t="str">
-        <x:v>SRC134_001</x:v>
+        <x:v>SRC260910_012</x:v>
       </x:c>
       <x:c r="B490" t="str">
-        <x:v>Strait of Hormuz Ship Monitor</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C490" t="str">
-        <x:v>Monthly AIS-derived Strait crossing statistics; current month is partial and wartime AIS disruption makes counts conservative lower bounds.</x:v>
+        <x:v>Newcastle gets $1.62bn freight access upgrade</x:v>
       </x:c>
       <x:c r="D490" t="str">
-        <x:v>https://hormuz.data-tracking.net/stats</x:v>
+        <x:v>https://splash247.com/newcastle-gets-1-62bn-freight-access-upgrade/</x:v>
       </x:c>
       <x:c r="E490" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F490" t="str">
-        <x:v>Public data / CC BY 4.0</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
       <x:c r="A491" t="str">
-        <x:v>SRC134_002</x:v>
+        <x:v>SRC260910_013</x:v>
       </x:c>
       <x:c r="B491" t="str">
-        <x:v>Strait of Hormuz Ship Monitor</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C491" t="str">
-        <x:v>Free public JSON/CSV API documentation; 30-minute AIS polling, 90-day history and no API key.</x:v>
+        <x:v>Baltimore adds on-dock grain export gateway</x:v>
       </x:c>
       <x:c r="D491" t="str">
-        <x:v>https://hormuz.data-tracking.net/api-docs</x:v>
+        <x:v>https://splash247.com/baltimore-adds-on-dock-grain-export-gateway/</x:v>
       </x:c>
       <x:c r="E491" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F491" t="str">
-        <x:v>Public API documentation / CC BY 4.0</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
       <x:c r="A492" t="str">
-        <x:v>SRC134_003</x:v>
+        <x:v>SRC260910_014</x:v>
       </x:c>
       <x:c r="B492" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C492" t="str">
-        <x:v>Hunter Group says a counterparty owes USD 55 million amid a tanker-rate benchmark dispute.</x:v>
+        <x:v>Kazakhstan advances $1bn Caspian port hub</x:v>
       </x:c>
       <x:c r="D492" t="str">
-        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+        <x:v>https://splash247.com/kazakhstan-advances-1bn-caspian-port-hub/</x:v>
       </x:c>
       <x:c r="E492" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F492" t="str">
-        <x:v>Trade press</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
       <x:c r="A493" t="str">
-        <x:v>SRC134_004</x:v>
+        <x:v>SRC260910_015</x:v>
       </x:c>
       <x:c r="B493" t="str">
-        <x:v>Seaspan</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C493" t="str">
-        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
+        <x:v>Valencia north terminal survives environmental court challenge</x:v>
       </x:c>
       <x:c r="D493" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+        <x:v>https://splash247.com/valencia-north-terminal-survives-environmental-court-challenge/</x:v>
       </x:c>
       <x:c r="E493" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F493" t="str">
-        <x:v>Official company release</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
       <x:c r="A494" t="str">
-        <x:v>SRC134_005</x:v>
+        <x:v>SRC260910_016</x:v>
       </x:c>
       <x:c r="B494" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C494" t="str">
-        <x:v>MSC Shipmanagement and Hong Kong Spirit Shipping and Trading fined USD 1.75 million over illegal oily-waste discharges from MSC SAMIRA III.</x:v>
+        <x:v>Manila South Harbour advances terminal expansion</x:v>
       </x:c>
       <x:c r="D494" t="str">
-        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+        <x:v>https://splash247.com/manila-south-harbour-advances-terminal-expansion/</x:v>
       </x:c>
       <x:c r="E494" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F494" t="str">
-        <x:v>Trade press / court reporting</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
       <x:c r="A495" t="str">
-        <x:v>SRC134_006</x:v>
+        <x:v>SRC260910_017</x:v>
       </x:c>
       <x:c r="B495" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C495" t="str">
-        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
+        <x:v>DP World formalises Mombasa industrial park joint venture</x:v>
       </x:c>
       <x:c r="D495" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+        <x:v>https://splash247.com/dp-world-formalises-mombasa-industrial-park-joint-venture/</x:v>
       </x:c>
       <x:c r="E495" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F495" t="str">
-        <x:v>Trade press / government-programme reporting</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
       <x:c r="A496" t="str">
-        <x:v>SRC134_007</x:v>
+        <x:v>SRC260910_018</x:v>
       </x:c>
       <x:c r="B496" t="str">
-        <x:v>gCaptain</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C496" t="str">
-        <x:v>Arctic LNG 2 seeks about USD 1 billion from Hanwha Ocean in a shipbuilding-contract dispute.</x:v>
+        <x:v>Adani lands 30-year Paradip berth concession</x:v>
       </x:c>
       <x:c r="D496" t="str">
-        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
+        <x:v>https://splash247.com/adani-lands-30-year-paradip-berth-concession/</x:v>
       </x:c>
       <x:c r="E496" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F496" t="str">
-        <x:v>Trade press / Reuters syndication</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
       <x:c r="A497" t="str">
-        <x:v>SRC134_008</x:v>
+        <x:v>SRC260910_019</x:v>
       </x:c>
       <x:c r="B497" t="str">
-        <x:v>Reuters</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="C497" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
+        <x:v>Odfjell Drilling lands $518m semisub deal with Vår Energi</x:v>
       </x:c>
       <x:c r="D497" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+        <x:v>https://splash247.com/odfjell-drilling-lands-518m-semisub-deal-with-var-energi/</x:v>
       </x:c>
       <x:c r="E497" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="F497" t="str">
-        <x:v>News / legal and energy reporting</x:v>
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
-      <x:c r="A498" s="14" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="B498" s="14" t="str">
-        <x:v>Power &amp; Corridors</x:v>
-      </x:c>
-      <x:c r="C498" s="14" t="str">
-        <x:v>PGSA blacklist reference, vessel identities, list expansion and STS exposure</x:v>
-      </x:c>
-      <x:c r="D498" s="14" t="str">
-        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
-      </x:c>
-      <x:c r="E498" s="14" t="str">
+      <x:c r="A498" t="str">
+        <x:v>SRC260910_020</x:v>
+      </x:c>
+      <x:c r="B498" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C498" t="str">
+        <x:v>Alam Maritim head faces fraud charges tied to vessel rates</x:v>
+      </x:c>
+      <x:c r="D498" t="str">
+        <x:v>https://splash247.com/alam-maritim-head-faces-fraud-charges-tied-to-vessel-rates/</x:v>
+      </x:c>
+      <x:c r="E498" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F498" s="14" t="str">
-        <x:v>P&amp;C analysis / curated source</x:v>
+      <x:c r="F498" t="str">
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
-      <x:c r="A499" s="14" t="str">
-        <x:v>SRC_JCG</x:v>
-      </x:c>
-      <x:c r="B499" s="14" t="str">
-        <x:v>Japan Coast Guard</x:v>
-      </x:c>
-      <x:c r="C499" s="14" t="str">
-        <x:v>Official Japan Coast Guard press releases, foreign-vessel rescue updates and navigational information</x:v>
-      </x:c>
-      <x:c r="D499" s="14" t="str">
-        <x:v>https://www.kaiho.mlit.go.jp/e/topics_archive/index.html</x:v>
-      </x:c>
-      <x:c r="E499" s="14" t="str">
+      <x:c r="A499" t="str">
+        <x:v>SRC260910_021</x:v>
+      </x:c>
+      <x:c r="B499" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C499" t="str">
+        <x:v>Ernst Russ doubles down on tankers with Cargill-backed pair</x:v>
+      </x:c>
+      <x:c r="D499" t="str">
+        <x:v>https://splash247.com/ernst-russ-doubles-down-on-tankers-with-cargill-backed-pair/</x:v>
+      </x:c>
+      <x:c r="E499" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F499" s="14" t="str">
-        <x:v>Official / primary source</x:v>
+      <x:c r="F499" t="str">
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
-      <x:c r="A500" s="14" t="str">
-        <x:v>SRC_KCG</x:v>
-      </x:c>
-      <x:c r="B500" s="14" t="str">
-        <x:v>Korea Coast Guard</x:v>
-      </x:c>
-      <x:c r="C500" s="14" t="str">
-        <x:v>Official Korea Coast Guard national/regional press releases and maritime incident reporting</x:v>
-      </x:c>
-      <x:c r="D500" s="14" t="str">
-        <x:v>https://www.kcg.go.kr/</x:v>
-      </x:c>
-      <x:c r="E500" s="14" t="str">
+      <x:c r="A500" t="str">
+        <x:v>SRC260910_022</x:v>
+      </x:c>
+      <x:c r="B500" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C500" t="str">
+        <x:v>CMA CGM says it met obligations in $186m Samsung dispute</x:v>
+      </x:c>
+      <x:c r="D500" t="str">
+        <x:v>https://splash247.com/cma-cgm-says-it-met-obligations-in-186m-samsung-dispute/</x:v>
+      </x:c>
+      <x:c r="E500" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F500" s="14" t="str">
-        <x:v>Official / primary source</x:v>
+      <x:c r="F500" t="str">
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
-      <x:c r="A501" s="14" t="str">
-        <x:v>SRC_ICG</x:v>
-      </x:c>
-      <x:c r="B501" s="14" t="str">
-        <x:v>Indian Coast Guard</x:v>
-      </x:c>
-      <x:c r="C501" s="14" t="str">
-        <x:v>Official Indian Coast Guard news, SAR, pollution response and maritime assistance</x:v>
-      </x:c>
-      <x:c r="D501" s="14" t="str">
-        <x:v>https://indiancoastguard.gov.in/</x:v>
-      </x:c>
-      <x:c r="E501" s="14" t="str">
+      <x:c r="A501" t="str">
+        <x:v>SRC260910_023</x:v>
+      </x:c>
+      <x:c r="B501" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C501" t="str">
+        <x:v>Safe Bulkers raises $94m for fleet push</x:v>
+      </x:c>
+      <x:c r="D501" t="str">
+        <x:v>https://splash247.com/safe-bulkers-raises-94m-for-fleet-push/</x:v>
+      </x:c>
+      <x:c r="E501" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F501" s="14" t="str">
-        <x:v>Official / primary source</x:v>
+      <x:c r="F501" t="str">
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
-      <x:c r="A502" s="14" t="str">
-        <x:v>SRC_DGS_INDIA</x:v>
-      </x:c>
-      <x:c r="B502" s="14" t="str">
-        <x:v>Directorate General of Shipping India</x:v>
-      </x:c>
-      <x:c r="C502" s="14" t="str">
-        <x:v>Official casualty investigation circulars and marine safety guidance</x:v>
-      </x:c>
-      <x:c r="D502" s="14" t="str">
-        <x:v>https://www.dgshipping.gov.in/</x:v>
-      </x:c>
-      <x:c r="E502" s="14" t="str">
+      <x:c r="A502" t="str">
+        <x:v>SRC260910_024</x:v>
+      </x:c>
+      <x:c r="B502" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C502" t="str">
+        <x:v>Hormuz attacks reach wartime high</x:v>
+      </x:c>
+      <x:c r="D502" t="str">
+        <x:v>https://splash247.com/hormuz-attacks-reach-wartime-high/</x:v>
+      </x:c>
+      <x:c r="E502" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F502" s="14" t="str">
-        <x:v>Official / primary source</x:v>
+      <x:c r="F502" t="str">
+        <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
-      <x:c r="A503" s="14" t="str">
-        <x:v>SRC_SEC_GASLOG</x:v>
-      </x:c>
-      <x:c r="B503" s="14" t="str">
-        <x:v>Public vessel-reference sources</x:v>
-      </x:c>
-      <x:c r="C503" s="14" t="str">
-        <x:v>GasLog Shanghai identity/ownership sample used to test canonical vessel enrichment</x:v>
-      </x:c>
-      <x:c r="D503" s="14" t="str">
-        <x:v>https://www.shipspotting.com/photos/3877208</x:v>
-      </x:c>
-      <x:c r="E503" s="14" t="str">
+      <x:c r="A503" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="B503" t="str">
+        <x:v>Gulf News</x:v>
+      </x:c>
+      <x:c r="C503" t="str">
+        <x:v>Iran rocked by explosions as Trump says US-Iran war won't end until after midterm elections</x:v>
+      </x:c>
+      <x:c r="D503" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
+      </x:c>
+      <x:c r="E503" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F503" s="14" t="str">
-        <x:v>Secondary vessel-reference source</x:v>
+      <x:c r="F503" t="str">
+        <x:v>Regional news / security reporting</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
-      <x:c r="A504" s="14" t="str">
-        <x:v>SRC_SEC_ALREK</x:v>
-      </x:c>
-      <x:c r="B504" s="14" t="str">
-        <x:v>Public vessel-reference sources</x:v>
-      </x:c>
-      <x:c r="C504" s="14" t="str">
-        <x:v>Al Rekayyat identity/ownership sample used to test canonical vessel enrichment</x:v>
-      </x:c>
-      <x:c r="D504" s="14" t="str">
-        <x:v>https://www.ship-db.de/nawbn.php?wbn_nr=hyhu1910010E</x:v>
-      </x:c>
-      <x:c r="E504" s="14" t="str">
+      <x:c r="A504" t="str">
+        <x:v>SRC260910_026</x:v>
+      </x:c>
+      <x:c r="B504" t="str">
+        <x:v>OC Media</x:v>
+      </x:c>
+      <x:c r="C504" t="str">
+        <x:v>Two Azerbaijani citizens killed in drone attack on cargo ship in Black Sea / Sea of Azov</x:v>
+      </x:c>
+      <x:c r="D504" t="str">
+        <x:v>https://oc-media.org/two-azerbaijani-citizens-killed-in-drone-attack-on-cargo-ship-in-black-sea/</x:v>
+      </x:c>
+      <x:c r="E504" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
-      <x:c r="F504" s="14" t="str">
-        <x:v>Secondary vessel-reference source</x:v>
+      <x:c r="F504" t="str">
+        <x:v>Regional news / maritime security</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" t="str">
+        <x:v>SRC260910_027</x:v>
+      </x:c>
+      <x:c r="B505" t="str">
+        <x:v>OilPrice.com</x:v>
+      </x:c>
+      <x:c r="C505" t="str">
+        <x:v>Ukraine Targets Russia's Key Black Sea Oil Port</x:v>
+      </x:c>
+      <x:c r="D505" t="str">
+        <x:v>https://oilprice.com/Latest-Energy-News/World-News/Ukraine-Targets-Russias-Key-Black-Sea-Oil-Port.html</x:v>
+      </x:c>
+      <x:c r="E505" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F505" t="str">
+        <x:v>Energy / maritime security reporting</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10566,230 +10586,6 @@
         <x:v>Use source lineage.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>FEED134_001</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>Strait of Hormuz Ship Monitor API</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>https://hormuz.data-tracking.net/api/summary?hours=24</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Hormuz crossings; ships by zone; daily traffic; oil/gas export estimates</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Security; trade flow; energy; chokepoint</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>Deduplicate by endpoint, UTC period and vessel/crossing identifier</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>Public JSON/CSV API; no key; poll no faster than source's 30-minute AIS refresh; CC BY 4.0.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>FEED_SEC_001</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>Japan Coast Guard – Press Releases</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>https://www.kaiho.mlit.go.jp/e/topics_archive/index.html</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>Japan / surrounding waters</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>Maritime casualty; SAR; navigation warning; pollution; enforcement</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I8" s="14" t="str">
-        <x:v>Deduplicate by date + vessel/incident + official update number</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="str">
-        <x:v>Primary MARSEC monitoring feed.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>FEED_SEC_002</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>Japan Coast Guard – Foreign Vessel Rescue</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>https://www.kaiho.mlit.go.jp/info/topics/rescueforeignvessels.html</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>Japan / high seas around Japan</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>SAR; crew injury; missing person; distressed vessel</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I9" s="14" t="str">
-        <x:v>Resolve vessel by IMO/name before canonical event creation</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="str">
-        <x:v>Useful structured foreign-vessel incident index.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>FEED_SEC_003</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>Korea Coast Guard – Press Releases</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>https://www.kcg.go.kr/</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>South Korea / Korean waters</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>Grounding; collision; SAR; pollution; enforcement; maritime security</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H10" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I10" s="14" t="str">
-        <x:v>Deduplicate national/regional reposts by incident/date/location</x:v>
-      </x:c>
-      <x:c r="J10" s="14" t="str">
-        <x:v>Regional stations often publish incident detail first.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="14" t="str">
-        <x:v>FEED_SEC_004</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="str">
-        <x:v>Indian Coast Guard – News &amp; Assistance</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="str">
-        <x:v>https://indiancoastguard.gov.in/</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="str">
-        <x:v>India / Indian EEZ</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>SAR; vessel fire; grounding; pollution; maritime security; response</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H11" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I11" s="14" t="str">
-        <x:v>Resolve official incident to vessel/IMO and MRCC/region</x:v>
-      </x:c>
-      <x:c r="J11" s="14" t="str">
-        <x:v>Primary Indian MARSEC operational source.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="14" t="str">
-        <x:v>FEED_SEC_005</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>DG Shipping India – Casualty / Safety</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="str">
-        <x:v>https://www.dgshipping.gov.in/</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="str">
-        <x:v>India / Indian shipping</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="str">
-        <x:v>Marine casualty; casualty investigation; safety circular; regulatory response</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H12" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I12" s="14" t="str">
-        <x:v>Separate casualty occurrence from later safety circular/investigation</x:v>
-      </x:c>
-      <x:c r="J12" s="14" t="str">
-        <x:v>Primary regulatory/casualty source.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="14" t="str">
-        <x:v>FEED_SEC_006</x:v>
-      </x:c>
-      <x:c r="B13" s="14" t="str">
-        <x:v>PGSA Compliance Monitor</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="str">
-        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
-      </x:c>
-      <x:c r="D13" s="14" t="str">
-        <x:v>Strait of Hormuz / Gulf / Oman approaches</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="str">
-        <x:v>Compliance restriction; designation; STS exposure; enforcement; delisting</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H13" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="I13" s="14" t="str">
-        <x:v>IMO-first; do not merge PGSA with OFAC/EU/UK legal sanctions</x:v>
-      </x:c>
-      <x:c r="J13" s="14" t="str">
-        <x:v>P&amp;C curated monitor pending primary PGSA machine-readable source.</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re80f78c2bf5146ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rf10aef9e4d06453c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R6ab768ad7c664d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R5a62ad51c805425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R3f722a3f90fd4146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="Rb370ba0a60644c70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10373,6 +10373,166 @@
         <x:v>Energy / maritime security reporting</x:v>
       </x:c>
     </x:row>
+    <x:row r="506">
+      <x:c r="A506" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+      <x:c r="B506" s="14" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C506" s="14" t="str">
+        <x:v>Qingdao Beihai shipyard fire / Ocean Melody casualty and yard capacity</x:v>
+      </x:c>
+      <x:c r="D506" s="14" t="str">
+        <x:v>https://www.reuters.com/world/asia-pacific/fire-cargo-vessel-china-shipyard-causes-major-casualties-state-media-reports-2026-09-10/</x:v>
+      </x:c>
+      <x:c r="E506" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F506" s="14" t="str">
+        <x:v>News / primary reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507" s="14" t="str">
+        <x:v>SRC260911_002</x:v>
+      </x:c>
+      <x:c r="B507" s="14" t="str">
+        <x:v>Rynda / vessel particulars</x:v>
+      </x:c>
+      <x:c r="C507" s="14" t="str">
+        <x:v>Ocean Melody IMO 9303065 vessel particulars</x:v>
+      </x:c>
+      <x:c r="D507" s="14" t="str">
+        <x:v>https://rynda.com/vessels/ocean-melody/</x:v>
+      </x:c>
+      <x:c r="E507" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F507" s="14" t="str">
+        <x:v>Vessel reference</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508" s="14" t="str">
+        <x:v>SRC260911_003</x:v>
+      </x:c>
+      <x:c r="B508" s="14" t="str">
+        <x:v>International Maritime Organization</x:v>
+      </x:c>
+      <x:c r="C508" s="14" t="str">
+        <x:v>Middle East - Highlighted (Confirmed) incidents</x:v>
+      </x:c>
+      <x:c r="D508" s="14" t="str">
+        <x:v>https://www.imo.org/en/mediacentre/hottopics/pages/middle-east-highlighted-incidents.aspx</x:v>
+      </x:c>
+      <x:c r="E508" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F508" s="14" t="str">
+        <x:v>Official / institutional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509" s="14" t="str">
+        <x:v>SRC260911_004</x:v>
+      </x:c>
+      <x:c r="B509" s="14" t="str">
+        <x:v>International Maritime Organization</x:v>
+      </x:c>
+      <x:c r="C509" s="14" t="str">
+        <x:v>Red Sea area maritime security baseline</x:v>
+      </x:c>
+      <x:c r="D509" s="14" t="str">
+        <x:v>https://www.imo.org/en/mediacentre/hottopics/pages/red-sea.aspx</x:v>
+      </x:c>
+      <x:c r="E509" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F509" s="14" t="str">
+        <x:v>Official / institutional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510" s="14" t="str">
+        <x:v>SRC260911_005</x:v>
+      </x:c>
+      <x:c r="B510" s="14" t="str">
+        <x:v>International Maritime Organization</x:v>
+      </x:c>
+      <x:c r="C510" s="14" t="str">
+        <x:v>Operational FAQs – IMO Strait of Hormuz Evacuation Plan</x:v>
+      </x:c>
+      <x:c r="D510" s="14" t="str">
+        <x:v>https://www.imo.org/en/mediacentre/hottopics/pages/faqs-strait-of-hormuz-evacuation-plan.aspx</x:v>
+      </x:c>
+      <x:c r="E510" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F510" s="14" t="str">
+        <x:v>Official / institutional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" s="14" t="str">
+        <x:v>SRC260911_006</x:v>
+      </x:c>
+      <x:c r="B511" s="14" t="str">
+        <x:v>International Maritime Organization</x:v>
+      </x:c>
+      <x:c r="C511" s="14" t="str">
+        <x:v>Safety of straits used for international navigation - FAQs</x:v>
+      </x:c>
+      <x:c r="D511" s="14" t="str">
+        <x:v>https://www.imo.org/en/mediacentre/hottopics/pages/faq-safety-of-straits-used-for-international-navigation-.aspx</x:v>
+      </x:c>
+      <x:c r="E511" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F511" s="14" t="str">
+        <x:v>Official / institutional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" s="14" t="str">
+        <x:v>SRC260911_007</x:v>
+      </x:c>
+      <x:c r="B512" s="14" t="str">
+        <x:v>International Maritime Organization</x:v>
+      </x:c>
+      <x:c r="C512" s="14" t="str">
+        <x:v>Maritime Security and Safety in the Black Sea and Sea of Azov</x:v>
+      </x:c>
+      <x:c r="D512" s="14" t="str">
+        <x:v>https://www.imo.org/en/mediacentre/hottopics/pages/maritimesecurityandsafetyintheblackseaandseaofazov.aspx</x:v>
+      </x:c>
+      <x:c r="E512" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F512" s="14" t="str">
+        <x:v>Official / institutional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" s="14" t="str">
+        <x:v>SRC260911_008</x:v>
+      </x:c>
+      <x:c r="B513" s="14" t="str">
+        <x:v>The Signal Group</x:v>
+      </x:c>
+      <x:c r="C513" s="14" t="str">
+        <x:v>Weekly Dry Market Monitor: Week 36, 2026</x:v>
+      </x:c>
+      <x:c r="D513" s="14" t="str">
+        <x:v>https://www.thesignalgroup.com/weekly-market-monitor/weekly-dry-market-monitor-week-36-2026</x:v>
+      </x:c>
+      <x:c r="E513" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F513" s="14" t="str">
+        <x:v>Industry market monitor</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Refa47a01fe8641a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rb249bd4dcc8c45a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R818a9225cfde442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Ra016bce5f0c2416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R05fed96c02df4a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R67504e7b95c74fad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11238,6 +11238,186 @@
         <x:v>Issuer / primary source</x:v>
       </x:c>
     </x:row>
+    <x:row r="544">
+      <x:c r="A544" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+      <x:c r="B544" t="str">
+        <x:v>Press Information Bureau, Government of India</x:v>
+      </x:c>
+      <x:c r="C544" t="str">
+        <x:v>ORV Sagar Manthan launch; NCPOR/MoES ownership context; Deep Ocean Mission; launch milestones; 2028 delivery target</x:v>
+      </x:c>
+      <x:c r="D544" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+      <x:c r="E544" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F544" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545">
+      <x:c r="A545" t="str">
+        <x:v>SRC_SAGAR_GRSE_CONTRACT</x:v>
+      </x:c>
+      <x:c r="B545" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C545" t="str">
+        <x:v>16 Jul 2024 ₹840 crore NCPOR ORV contract; Yard 3041 specifications and mission capabilities</x:v>
+      </x:c>
+      <x:c r="D545" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+      <x:c r="E545" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F545" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546">
+      <x:c r="A546" t="str">
+        <x:v>SRC_SAGAR_NCPOR_KANYA</x:v>
+      </x:c>
+      <x:c r="B546" t="str">
+        <x:v>National Centre for Polar and Ocean Research (NCPOR)</x:v>
+      </x:c>
+      <x:c r="C546" t="str">
+        <x:v>ORV Sagar Kanya history, 1983 delivery, diesel-electric / DP platform, dimensions and research role</x:v>
+      </x:c>
+      <x:c r="D546" t="str">
+        <x:v>https://ncpor.res.in/pages/view/260/167-orv-sagar-kanya</x:v>
+      </x:c>
+      <x:c r="E546" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F546" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547">
+      <x:c r="A547" t="str">
+        <x:v>SRC_SAGAR_NCPOR_KANYA_TOW</x:v>
+      </x:c>
+      <x:c r="B547" t="str">
+        <x:v>National Centre for Polar and Ocean Research (NCPOR)</x:v>
+      </x:c>
+      <x:c r="C547" t="str">
+        <x:v>Current Sagar Kanya registry particulars: IMO 8123183; India/Mumbai; President of India represented by MoES; GT 4888; dimensions</x:v>
+      </x:c>
+      <x:c r="D547" t="str">
+        <x:v>https://ncpor.res.in/upload/tenders/NCPOR_VOM-12016_2_2025.PDF</x:v>
+      </x:c>
+      <x:c r="E547" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F547" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548">
+      <x:c r="A548" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+      <x:c r="B548" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C548" t="str">
+        <x:v>29 Oct 2024 ₹490.98 crore Acoustic Research Ship contract for NPOL/DRDO; 90m x 14m; 4-12 knots; 30-day/4,500nm endurance; 70 personnel</x:v>
+      </x:c>
+      <x:c r="D548" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+      <x:c r="E548" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F548" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549">
+      <x:c r="A549" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS_START</x:v>
+      </x:c>
+      <x:c r="B549" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C549" t="str">
+        <x:v>16 Apr 2025 construction commencement for NPOL/DRDO Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="D549" t="str">
+        <x:v>https://www.grse.in/press-releases-2025-26-quarter1/</x:v>
+      </x:c>
+      <x:c r="E549" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F549" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550">
+      <x:c r="A550" t="str">
+        <x:v>SRC_SAGAR_GRSE_AR2025</x:v>
+      </x:c>
+      <x:c r="B550" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C550" t="str">
+        <x:v>Annual report confirms ORV order ₹840 crore, ARS order ₹490.98 crore, Yard 3041 / Yard 3058 programme references</x:v>
+      </x:c>
+      <x:c r="D550" t="str">
+        <x:v>https://www.grse.in/annual-reports/Annual%20Report%202024-25.pdf</x:v>
+      </x:c>
+      <x:c r="E550" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F550" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551">
+      <x:c r="A551" t="str">
+        <x:v>SRC_SAGAR_FX_20240716</x:v>
+      </x:c>
+      <x:c r="B551" t="str">
+        <x:v>Historical FX reference</x:v>
+      </x:c>
+      <x:c r="C551" t="str">
+        <x:v>USD/INR historical rate used for ORV normalization: ₹83.58 per USD on 16 Jul 2024</x:v>
+      </x:c>
+      <x:c r="D551" t="str">
+        <x:v>https://www.exchange-rates.org/exchange-rate-history/usd-inr-2024-07-16</x:v>
+      </x:c>
+      <x:c r="E551" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F551" t="str">
+        <x:v>Market data / historical FX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552">
+      <x:c r="A552" t="str">
+        <x:v>SRC_SAGAR_FX_20241029</x:v>
+      </x:c>
+      <x:c r="B552" t="str">
+        <x:v>Historical FX reference</x:v>
+      </x:c>
+      <x:c r="C552" t="str">
+        <x:v>USD/INR historical rate used for ARS normalization: ₹84.06594 per USD on 29 Oct 2024</x:v>
+      </x:c>
+      <x:c r="D552" t="str">
+        <x:v>https://www.exchange-rates.org/exchange-rate-history/usd-inr-2024-10-29</x:v>
+      </x:c>
+      <x:c r="E552" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F552" t="str">
+        <x:v>Market data / historical FX</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/10_sources_evidence.xlsx
+++ b/data/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Ra016bce5f0c2416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R05fed96c02df4a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R67504e7b95c74fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb468eafe73f34cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R368a63985edd44eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R92519211a0a54fc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11418,6 +11418,246 @@
         <x:v>Market data / historical FX</x:v>
       </x:c>
     </x:row>
+    <x:row r="553">
+      <x:c r="A553" t="str">
+        <x:v>SRC_SEC_001</x:v>
+      </x:c>
+      <x:c r="B553" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C553" t="str">
+        <x:v>Houthi capture of Mokha; proximity to Bab al-Mandab; shipping and trade implications</x:v>
+      </x:c>
+      <x:c r="D553" t="str">
+        <x:v>https://splash247.com/houthis-advance-towards-bab-al-mandab-with-capture-of-mokha/</x:v>
+      </x:c>
+      <x:c r="E553" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F553" t="str">
+        <x:v>Specialist trade press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554">
+      <x:c r="A554" t="str">
+        <x:v>SRC_SEC_002</x:v>
+      </x:c>
+      <x:c r="B554" t="str">
+        <x:v>Reuters via gCaptain</x:v>
+      </x:c>
+      <x:c r="C554" t="str">
+        <x:v>Houthi seizure of Mocha and advance to Hanish islands; statement on navigation</x:v>
+      </x:c>
+      <x:c r="D554" t="str">
+        <x:v>https://gcaptain.com/houthis-seize-mocha-tightening-grip-on-bab-el-mandeb-and-red-sea-shipping/</x:v>
+      </x:c>
+      <x:c r="E554" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F554" t="str">
+        <x:v>Major reporting / secondary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555">
+      <x:c r="A555" t="str">
+        <x:v>SRC_SEC_003</x:v>
+      </x:c>
+      <x:c r="B555" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C555" t="str">
+        <x:v>Attempted pirate boarding of GLAMOR off Yemen; route, manager, crew outcome</x:v>
+      </x:c>
+      <x:c r="D555" t="str">
+        <x:v>https://splash247.com/pirates-board-ship-off-yemen/</x:v>
+      </x:c>
+      <x:c r="E555" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F555" t="str">
+        <x:v>Specialist trade press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556">
+      <x:c r="A556" t="str">
+        <x:v>SRC_SEC_004</x:v>
+      </x:c>
+      <x:c r="B556" t="str">
+        <x:v>Klaipėda State Seaport Authority</x:v>
+      </x:c>
+      <x:c r="C556" t="str">
+        <x:v>Smart buoy deployment and operational response to GPS disruption</x:v>
+      </x:c>
+      <x:c r="D556" t="str">
+        <x:v>https://portofklaipeda.lt/en/naujienos/smarter-and-safer-navigation-new-buoy-begins-operating-near-the-port-of-klaipeda/</x:v>
+      </x:c>
+      <x:c r="E556" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F556" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557">
+      <x:c r="A557" t="str">
+        <x:v>SRC_SEC_005</x:v>
+      </x:c>
+      <x:c r="B557" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C557" t="str">
+        <x:v>Indefinite strike at Terminal Cuenca del Plata and restrictions on container handling</x:v>
+      </x:c>
+      <x:c r="D557" t="str">
+        <x:v>https://splash247.com/indefinite-strike-hits-montevideo-container-terminal/</x:v>
+      </x:c>
+      <x:c r="E557" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F557" t="str">
+        <x:v>Specialist trade press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558">
+      <x:c r="A558" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="B558" t="str">
+        <x:v>International Railway Journal</x:v>
+      </x:c>
+      <x:c r="C558" t="str">
+        <x:v>Mounting Russian attacks on Ukrainian locomotives, depots and rail infrastructure</x:v>
+      </x:c>
+      <x:c r="D558" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+      <x:c r="E558" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F558" t="str">
+        <x:v>Specialist rail press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559">
+      <x:c r="A559" t="str">
+        <x:v>SRC_SEC_007</x:v>
+      </x:c>
+      <x:c r="B559" t="str">
+        <x:v>Ukrzaliznytsia</x:v>
+      </x:c>
+      <x:c r="C559" t="str">
+        <x:v>Darnytsia locomotive-depot ballistic missile strike and employee fatality</x:v>
+      </x:c>
+      <x:c r="D559" t="str">
+        <x:v>https://zalizna-rodyna.uz.gov.ua/en/memorial/volodimir-gubskiy</x:v>
+      </x:c>
+      <x:c r="E559" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F559" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560">
+      <x:c r="A560" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+      <x:c r="B560" t="str">
+        <x:v>Air Cargo Week</x:v>
+      </x:c>
+      <x:c r="C560" t="str">
+        <x:v>NATS technical failure; ~1,300 cancellations; network recovery and no cyberattack finding</x:v>
+      </x:c>
+      <x:c r="D560" t="str">
+        <x:v>https://aircargoweek.com/nats-system-failure-leaves-uk-airlines-battling-a-second-day-of-disruption/</x:v>
+      </x:c>
+      <x:c r="E560" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F560" t="str">
+        <x:v>Specialist air-cargo press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561">
+      <x:c r="A561" t="str">
+        <x:v>SRC_SEC_009</x:v>
+      </x:c>
+      <x:c r="B561" t="str">
+        <x:v>Air Cargo Week</x:v>
+      </x:c>
+      <x:c r="C561" t="str">
+        <x:v>Kenya aviation strike; JKIA cargo concentration and perishables trade exposure</x:v>
+      </x:c>
+      <x:c r="D561" t="str">
+        <x:v>https://aircargoweek.com/kenya-aviation-strike-exposes-the-fragility-of-east-africas-air-cargo-gateway/</x:v>
+      </x:c>
+      <x:c r="E561" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F561" t="str">
+        <x:v>Specialist air-cargo press</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562">
+      <x:c r="A562" t="str">
+        <x:v>SRC_SEC_010</x:v>
+      </x:c>
+      <x:c r="B562" t="str">
+        <x:v>Maritime and Port Authority of Singapore</x:v>
+      </x:c>
+      <x:c r="C562" t="str">
+        <x:v>Port Marine Circular 10/2026 on accurate vessel identity, ownership, cargo and trading-history filings</x:v>
+      </x:c>
+      <x:c r="D562" t="str">
+        <x:v>https://www.mpa.gov.sg/media-centre</x:v>
+      </x:c>
+      <x:c r="E562" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F562" t="str">
+        <x:v>Official / primary source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563">
+      <x:c r="A563" t="str">
+        <x:v>SRC_SEC_011</x:v>
+      </x:c>
+      <x:c r="B563" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="C563" t="str">
+        <x:v>Fraudulent registries, false AIS meetings and GPS jamming as sanctions-screening risks</x:v>
+      </x:c>
+      <x:c r="D563" t="str">
+        <x:v>https://shipandbunker.com/news/world/312418-feature-bunker-suppliers-can-no-longer-trust-two-key-sanctions-checks</x:v>
+      </x:c>
+      <x:c r="E563" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F563" t="str">
+        <x:v>Specialist trade press / risk analysis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564">
+      <x:c r="A564" t="str">
+        <x:v>SRC_SEC_012</x:v>
+      </x:c>
+      <x:c r="B564" t="str">
+        <x:v>Air Cargo Week</x:v>
+      </x:c>
+      <x:c r="C564" t="str">
+        <x:v>NTSB statement / Miami cargo aircraft crash and investigation</x:v>
+      </x:c>
+      <x:c r="D564" t="str">
+        <x:v>https://aircargoweek.com/ntsb-issues-statement-on-miami-cargo-aircraft-crash/</x:v>
+      </x:c>
+      <x:c r="E564" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F564" t="str">
+        <x:v>Specialist air-cargo press</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
